--- a/output/Muestreos_Activos.xlsx
+++ b/output/Muestreos_Activos.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1380" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1284" uniqueCount="360">
   <si>
     <t>ID</t>
   </si>
@@ -87,1081 +87,997 @@
     <t>Combinación</t>
   </si>
   <si>
+    <t>M02M109L03502-1B-0.7L</t>
+  </si>
+  <si>
+    <t>Arándano</t>
+  </si>
+  <si>
+    <t>02M109L03</t>
+  </si>
+  <si>
+    <t>NO LMC ( 100% )</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>En inventario</t>
+  </si>
+  <si>
+    <t>Activo</t>
+  </si>
+  <si>
+    <t>0.7 L</t>
+  </si>
+  <si>
+    <t>I22-M13-C912, I22-M01-C58, I22-M16-C2894</t>
+  </si>
+  <si>
+    <t>I22-M13-C912-V0.7 L-B1, I22-M01-C58-V0.7 L-B1, I22-M16-C2894-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>1 | 0.7 L</t>
+  </si>
+  <si>
+    <t>M04D002LI2603-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M02T105L03604-50B-0.143L</t>
+  </si>
+  <si>
+    <t>M02T106L03603-50B-0.143L</t>
+  </si>
+  <si>
+    <t>M02L008L11603-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M02M039L20604-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M02N042LB5601-1B-2.5L</t>
+  </si>
+  <si>
+    <t>M02N042LA5601-1B-2.5L</t>
+  </si>
+  <si>
+    <t>M02N042LC5601-1B-2.5L</t>
+  </si>
+  <si>
+    <t>M02T118LB5601-1B-0.6L</t>
+  </si>
+  <si>
+    <t>M02T114LA5602-1B-0.6L</t>
+  </si>
+  <si>
+    <t>M02T113LA5601-1B-0.6L</t>
+  </si>
+  <si>
+    <t>M02T119LA5601-1B-0.6L</t>
+  </si>
+  <si>
+    <t>M02T118LA5601-1B-0.6L</t>
+  </si>
+  <si>
+    <t>M02Q048L33604-1B-0.6L</t>
+  </si>
+  <si>
+    <t>M02Q047L24606-1B-0.6L</t>
+  </si>
+  <si>
+    <t>M02Q047LA5602-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q047L24605-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02M039L20603-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M02L008L11602-1B-1L</t>
+  </si>
+  <si>
+    <t>M02T105L03603-50B-0.143L</t>
+  </si>
+  <si>
+    <t>M02T083LA3601-50B-0.143L</t>
+  </si>
+  <si>
+    <t>M02T083LB4602-50B-0.143L</t>
+  </si>
+  <si>
+    <t>M04D002LF4602-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04B009LA5602-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04B009LA5601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LH2602-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LG2601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M06L004L13601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LF4601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LB4601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04A002LB2601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04L002L14601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LD4601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LM2604-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LI2602-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LI2601-1B-1L</t>
+  </si>
+  <si>
+    <t>M02U043L62601-1B-2.5L</t>
+  </si>
+  <si>
+    <t>M02U043L92601-1B-2.5L</t>
+  </si>
+  <si>
+    <t>M02U043L42601-1B-2.5L</t>
+  </si>
+  <si>
+    <t>M02Q048L33603-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q047L14602-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q047L24604-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M0601602-1B-1L</t>
+  </si>
+  <si>
+    <t>M04L002L23602-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02Q047LA5601-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q047L24602-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M04D002LM2602-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M04D002LM2602-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04L002L23601-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M04A002LA0602-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M02Q048L33601-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M04D002LH2601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M0601601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04A002LA0601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M04D002LM2601-1B-1.5L</t>
+  </si>
+  <si>
+    <t>M02Q050L01602-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q048L33515-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q048L13504-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M0240501-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02Q050L01526-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02Q047LA5502-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q068L24502-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q068L14501-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q050L01522-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02Q053L01504-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q068L01506-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q047L24511-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q047LA5501-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M0247518-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q047L24510-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02M022L02503-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02M040L33502-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02M040L13501-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02M040L23501-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02M078L02503-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02M110L03502-1B-0.7L</t>
+  </si>
+  <si>
+    <t>M02Q053L01503-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q048501-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q048L33511-1B-0.5L</t>
+  </si>
+  <si>
     <t>M02Q049L01504-1B-0.5L</t>
   </si>
   <si>
-    <t>Arándano</t>
+    <t>M02Q047L24508-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q048L33510-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02M039L20505-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02M022L02502-1B-0.5L</t>
+  </si>
+  <si>
+    <t>M02Q050L01521-1B-0.5L</t>
+  </si>
+  <si>
+    <t>Avellano</t>
+  </si>
+  <si>
+    <t>Cerezo</t>
+  </si>
+  <si>
+    <t>04D002LI2</t>
+  </si>
+  <si>
+    <t>02T105L03</t>
+  </si>
+  <si>
+    <t>02T106L03</t>
+  </si>
+  <si>
+    <t>02L008L11</t>
+  </si>
+  <si>
+    <t>02M039L20</t>
+  </si>
+  <si>
+    <t>02N042LB5</t>
+  </si>
+  <si>
+    <t>02N042LA5</t>
+  </si>
+  <si>
+    <t>02N042LC5</t>
+  </si>
+  <si>
+    <t>02T118LB5</t>
+  </si>
+  <si>
+    <t>02T114LA5</t>
+  </si>
+  <si>
+    <t>02T113LA5</t>
+  </si>
+  <si>
+    <t>02T119LA5</t>
+  </si>
+  <si>
+    <t>02T118LA5</t>
+  </si>
+  <si>
+    <t>02Q048L33</t>
+  </si>
+  <si>
+    <t>02Q047L24</t>
+  </si>
+  <si>
+    <t>02Q047LA5</t>
+  </si>
+  <si>
+    <t>02T083LA3</t>
+  </si>
+  <si>
+    <t>02T083LB4</t>
+  </si>
+  <si>
+    <t>04D002LF4</t>
+  </si>
+  <si>
+    <t>04B009LA5</t>
+  </si>
+  <si>
+    <t>04D002LH2</t>
+  </si>
+  <si>
+    <t>04D002LG2</t>
+  </si>
+  <si>
+    <t>06L004L13</t>
+  </si>
+  <si>
+    <t>04D002LB4</t>
+  </si>
+  <si>
+    <t>04A002LB2</t>
+  </si>
+  <si>
+    <t>04L002L14</t>
+  </si>
+  <si>
+    <t>04D002LD4</t>
+  </si>
+  <si>
+    <t>04D002LM2</t>
+  </si>
+  <si>
+    <t>02U043L62</t>
+  </si>
+  <si>
+    <t>02U043L92</t>
+  </si>
+  <si>
+    <t>02U043L42</t>
+  </si>
+  <si>
+    <t>02Q047L14</t>
+  </si>
+  <si>
+    <t>0601</t>
+  </si>
+  <si>
+    <t>04L002L23</t>
+  </si>
+  <si>
+    <t>04A002LA0</t>
+  </si>
+  <si>
+    <t>02Q050L01</t>
+  </si>
+  <si>
+    <t>02Q048L13</t>
+  </si>
+  <si>
+    <t>0240</t>
+  </si>
+  <si>
+    <t>02Q068L24</t>
+  </si>
+  <si>
+    <t>02Q068L14</t>
+  </si>
+  <si>
+    <t>02Q053L01</t>
+  </si>
+  <si>
+    <t>02Q068L01</t>
+  </si>
+  <si>
+    <t>0247</t>
+  </si>
+  <si>
+    <t>02M022L02</t>
+  </si>
+  <si>
+    <t>02M040L33</t>
+  </si>
+  <si>
+    <t>02M040L13</t>
+  </si>
+  <si>
+    <t>02M040L23</t>
+  </si>
+  <si>
+    <t>02M078L02</t>
+  </si>
+  <si>
+    <t>02M110L03</t>
+  </si>
+  <si>
+    <t>02Q048</t>
   </si>
   <si>
     <t>02Q049L01</t>
   </si>
   <si>
-    <t>NO LMC ( 100% )</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>En inventario</t>
-  </si>
-  <si>
-    <t>Activo</t>
+    <t>1.5 L</t>
+  </si>
+  <si>
+    <t>0.143 L</t>
+  </si>
+  <si>
+    <t>2.5 L</t>
+  </si>
+  <si>
+    <t>0.6 L</t>
   </si>
   <si>
     <t>0.5 L</t>
   </si>
   <si>
+    <t>1 L</t>
+  </si>
+  <si>
+    <t>I22-M10-C950</t>
+  </si>
+  <si>
+    <t>I13-M05-C14835</t>
+  </si>
+  <si>
+    <t>I13-M05-C920</t>
+  </si>
+  <si>
+    <t>I10-M04-C3000</t>
+  </si>
+  <si>
+    <t>I10-M02-C512, I10-M03-C6272, I10-M04-C763</t>
+  </si>
+  <si>
+    <t>I12-M06-C656</t>
+  </si>
+  <si>
+    <t>I12-M06-C848</t>
+  </si>
+  <si>
+    <t>I12-M06-C2168</t>
+  </si>
+  <si>
+    <t>I21-M07-C92</t>
+  </si>
+  <si>
+    <t>I21-M07-C204</t>
+  </si>
+  <si>
+    <t>I21-M07-C52</t>
+  </si>
+  <si>
+    <t>I21-M07-C64</t>
+  </si>
+  <si>
+    <t>I21-M07-C56</t>
+  </si>
+  <si>
+    <t>I12-M08-C6840, I21-M07-C1680, I12-M07-C8760, I21-M08-C1128</t>
+  </si>
+  <si>
+    <t>I12-M12-C5640, I12-M08-C2016</t>
+  </si>
+  <si>
+    <t>I10-M05-C960</t>
+  </si>
+  <si>
+    <t>I12-M09-C9120, I12-M10-C9120, I12-M11-C9120, I12-M12-C3480</t>
+  </si>
+  <si>
+    <t>I10-M01-C6272, I10-M02-C5728</t>
+  </si>
+  <si>
+    <t>I21-M07-C620</t>
+  </si>
+  <si>
+    <t>I21-M07-C750</t>
+  </si>
+  <si>
+    <t>I21-M07-C3318</t>
+  </si>
+  <si>
+    <t>I21-M07-C2836</t>
+  </si>
+  <si>
+    <t>I22-M10-C341</t>
+  </si>
+  <si>
+    <t>I22-M10-C1039</t>
+  </si>
+  <si>
+    <t>I22-M10-C690</t>
+  </si>
+  <si>
+    <t>I22-M11-C576, I22-M10-C647</t>
+  </si>
+  <si>
+    <t>I22-M11-C700</t>
+  </si>
+  <si>
+    <t>I20-M15-C2564, I20-M14-C1352</t>
+  </si>
+  <si>
+    <t>I22-M11-C2788</t>
+  </si>
+  <si>
+    <t>I22-M11-C115</t>
+  </si>
+  <si>
+    <t>I22-M11-C345</t>
+  </si>
+  <si>
+    <t>I22-M12-C53</t>
+  </si>
+  <si>
+    <t>I22-M12-C3488, I22-M11-C907</t>
+  </si>
+  <si>
+    <t>I22-M12-C360</t>
+  </si>
+  <si>
+    <t>I14-M11-C1200, I14-M10-C2128, I22-M12-C959</t>
+  </si>
+  <si>
+    <t>I14-M10-C500</t>
+  </si>
+  <si>
+    <t>I12-M05-C1523</t>
+  </si>
+  <si>
+    <t>I12-M05-C790</t>
+  </si>
+  <si>
+    <t>I12-M05-C1424</t>
+  </si>
+  <si>
+    <t>I21-M12-C5180, I21-M05-C8310, I21-M06-C8354, I21-M07-C2026</t>
+  </si>
+  <si>
+    <t>I21-M12-C349</t>
+  </si>
+  <si>
+    <t>I11-M11-C4920, I11-M12-C9120, I21-M10-C8318, I21-M11-C8256, I21-M12-C949, I21-M09-C8364</t>
+  </si>
+  <si>
+    <t>I20-M16-C1856, I20-M15-C3011</t>
+  </si>
+  <si>
+    <t>I22-M10-C5680, I22-M09-C5648, I22-M08-C4864</t>
+  </si>
+  <si>
+    <t>I22-MN17C4-C878</t>
+  </si>
+  <si>
+    <t>I10-MN07C3-C1304, I10-MN09C1-C10075, I22-MN16C3-C3123, I22-MN15C1-C5387, I22-MN06C1-C501, I22-MN05C4-C6504, I22-MN10C2-C4308, I22-MN12C1-C6861, I22-MN12C4-C7728, I22-MN13C1-C91, I22-MN13C4-C7633, I22-MN17C4-C5064, I22-MN18C1-C162, I22-MN20C2-C6012, I22-MN20C4-C753</t>
+  </si>
+  <si>
+    <t>I22-M08-C736, I22-M12-C680</t>
+  </si>
+  <si>
+    <t>I22-M14-C795</t>
+  </si>
+  <si>
+    <t>I22-M11-C5717, I22-M12-C5712, I22-M14-C2176</t>
+  </si>
+  <si>
+    <t>I22-M14-C300</t>
+  </si>
+  <si>
+    <t>I10-MN20C1-C2040, I10-MN20C2-C864, I10-MN20C3-C10224</t>
+  </si>
+  <si>
+    <t>I14-M15-C4352, I14-M06-C3920, I14-M07-C5851, I14-M08-C5793, I14-M12-C5983, I14-M11-C3696, I22-M13-C5712, I22-M14-C2333, I22-M15-C5664, I22-M16-C5696, I22-M09-C5792, I22-M10-C70</t>
+  </si>
+  <si>
+    <t>I20-M16-C207</t>
+  </si>
+  <si>
+    <t>I22-M10-C197</t>
+  </si>
+  <si>
+    <t>I14-M16-C6285, I14-M05-C5978, I14-M06-C1903, I14-M15-C1425</t>
+  </si>
+  <si>
+    <t>I21-M06-C360, I13-M01-C8479</t>
+  </si>
+  <si>
+    <t>I09-MN10C3-C580</t>
+  </si>
+  <si>
+    <t>I09-MN10C3-C552</t>
+  </si>
+  <si>
+    <t>I21-M09-C3313, I21-M03-C192</t>
+  </si>
+  <si>
+    <t>I13-M04-C2777</t>
+  </si>
+  <si>
+    <t>I22-MN05C3-C6329, I22-MN16C2-C5935</t>
+  </si>
+  <si>
+    <t>I22-M14-C480</t>
+  </si>
+  <si>
+    <t>I22-M14-C408</t>
+  </si>
+  <si>
+    <t>I22-M15-C139, I21-M01-C144, I21-M02-C72</t>
+  </si>
+  <si>
+    <t>I22-M14-C1392</t>
+  </si>
+  <si>
+    <t>I22-M14-C4256</t>
+  </si>
+  <si>
+    <t>I22-MN13C1-C1296, I22-MN12C3-C7948, I22-MN12C2-C5754, I22-MN12C1-C883, I22-MN11C4-C1080, I10-MN09C2-C9566, I10-MN10C2-C10190, I10-MN10C3-C289, I10-MN08C1-C5026, I10-MN10C1-C4966, I10-MN08C2-C1518, I10-MN09C3-C4896, I22-MN04C3-C6840, I22-MN04C4-C6639, I22-MN05C2-C6737, I22-MN06C4-C5163, I22-MN15C1-C910, I22-MN18C1-C1867</t>
+  </si>
+  <si>
+    <t>I22-MN13C4-C168, I22-MN12C4-C216, I22-MN12C3-C192, I22-MN16C4-C456</t>
+  </si>
+  <si>
+    <t>I22-MN16C2-C3480, I22-MN13C4-C1944, I22-MN12C4-C768, I22-MN12C3-C2568, I22-MN15C1-C8520, I22-MN14C4-C8520, I22-MN13C1-C5112, I22-MN14C3-C1080, I10-MN11C2-C24</t>
+  </si>
+  <si>
+    <t>I22-MN16C3-C1184, I22-MN12C4-C120, I22-MN15C1-C288</t>
+  </si>
+  <si>
+    <t>I22-M13-C1080, I22-M14-C327</t>
+  </si>
+  <si>
+    <t>I22-M13-C1224</t>
+  </si>
+  <si>
+    <t>I22-M13-C1194</t>
+  </si>
+  <si>
+    <t>I22-M13-C1059</t>
+  </si>
+  <si>
+    <t>I22-M13-C1387</t>
+  </si>
+  <si>
+    <t>I22-M13-C1495</t>
+  </si>
+  <si>
+    <t>I09-MN20C2-C265, I09-MN19C3-C1089, I09-MN20C3-C2880</t>
+  </si>
+  <si>
+    <t>I09-MN10C3-C2726</t>
+  </si>
+  <si>
+    <t>I09-MN06C3-C712, I09-MN10C3-C7034</t>
+  </si>
+  <si>
     <t>I22-M04-C12, I22-M01-C2, I22-M16-C137</t>
   </si>
   <si>
+    <t>I09-MN06C3-C709, I09-MN09C3-C694</t>
+  </si>
+  <si>
+    <t>I22-M01-C4, I10-MN20C2-C4387, I22-M16-C658</t>
+  </si>
+  <si>
+    <t>I09-MN02C1-C772</t>
+  </si>
+  <si>
+    <t>I09-MN03C1-C684, I09-MN05C2-C96, I09-MN05C3-C120, I09-MN04C3-C8424, I09-MN04C1-C2364</t>
+  </si>
+  <si>
+    <t>I22-MN05C2-C4312, I22-MN04C4-C3816, I22-MN05C1-C2</t>
+  </si>
+  <si>
+    <t>I22-M10-C950-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I13-M05-C14835-V0.143 L-B50</t>
+  </si>
+  <si>
+    <t>I13-M05-C920-V0.143 L-B50</t>
+  </si>
+  <si>
+    <t>I10-M04-C3000-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I10-M02-C512-V1.5 L-B1, I10-M03-C6272-V1.5 L-B1, I10-M04-C763-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M06-C656-V2.5 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M06-C848-V2.5 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M06-C2168-V2.5 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M07-C92-V0.6 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M07-C204-V0.6 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M07-C52-V0.6 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M07-C64-V0.6 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M07-C56-V0.6 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M08-C6840-V0.6 L-B1, I21-M07-C1680-V0.6 L-B1, I12-M07-C8760-V0.6 L-B1, I21-M08-C1128-V0.6 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M12-C5640-V0.6 L-B1, I12-M08-C2016-V0.6 L-B1</t>
+  </si>
+  <si>
+    <t>I10-M05-C960-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M09-C9120-V0.5 L-B1, I12-M10-C9120-V0.5 L-B1, I12-M11-C9120-V0.5 L-B1, I12-M12-C3480-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I10-M01-C6272-V1.5 L-B1, I10-M02-C5728-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M07-C620-V1 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M07-C750-V0.143 L-B50</t>
+  </si>
+  <si>
+    <t>I21-M07-C3318-V0.143 L-B50</t>
+  </si>
+  <si>
+    <t>I21-M07-C2836-V0.143 L-B50</t>
+  </si>
+  <si>
+    <t>I22-M10-C341-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M10-C1039-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M10-C690-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M11-C576-V1.5 L-B1, I22-M10-C647-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M11-C700-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I20-M15-C2564-V1.5 L-B1, I20-M14-C1352-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M11-C2788-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M11-C115-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M11-C345-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M12-C53-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M12-C3488-V1.5 L-B1, I22-M11-C907-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M12-C360-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I14-M11-C1200-V1.5 L-B1, I14-M10-C2128-V1.5 L-B1, I22-M12-C959-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I14-M10-C500-V1 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M05-C1523-V2.5 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M05-C790-V2.5 L-B1</t>
+  </si>
+  <si>
+    <t>I12-M05-C1424-V2.5 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M12-C5180-V0.5 L-B1, I21-M05-C8310-V0.5 L-B1, I21-M06-C8354-V0.5 L-B1, I21-M07-C2026-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M12-C349-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I11-M11-C4920-V0.5 L-B1, I11-M12-C9120-V0.5 L-B1, I21-M10-C8318-V0.5 L-B1, I21-M11-C8256-V0.5 L-B1, I21-M12-C949-V0.5 L-B1, I21-M09-C8364-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I20-M16-C1856-V1 L-B1, I20-M15-C3011-V1 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M10-C5680-V0.7 L-B1, I22-M09-C5648-V0.7 L-B1, I22-M08-C4864-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-MN17C4-C878-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I10-MN07C3-C1304-V0.5 L-B1, I10-MN09C1-C10075-V0.5 L-B1, I22-MN16C3-C3123-V0.5 L-B1, I22-MN15C1-C5387-V0.5 L-B1, I22-MN06C1-C501-V0.5 L-B1, I22-MN05C4-C6504-V0.5 L-B1, I22-MN10C2-C4308-V0.5 L-B1, I22-MN12C1-C6861-V0.5 L-B1, I22-MN12C4-C7728-V0.5 L-B1, I22-MN13C1-C91-V0.5 L-B1, I22-MN13C4-C7633-V0.5 L-B1, I22-MN17C4-C5064-V0.5 L-B1, I22-MN18C1-C162-V0.5 L-B1, I22-MN20C2-C6012-V0.5 L-B1, I22-MN20C4-C753-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M08-C736-V0.7 L-B1, I22-M12-C680-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M14-C795-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M11-C5717-V0.7 L-B1, I22-M12-C5712-V0.7 L-B1, I22-M14-C2176-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M14-C300-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I10-MN20C1-C2040-V0.5 L-B1, I10-MN20C2-C864-V0.5 L-B1, I10-MN20C3-C10224-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I14-M15-C4352-V1.5 L-B1, I14-M06-C3920-V1.5 L-B1, I14-M07-C5851-V1.5 L-B1, I14-M08-C5793-V1.5 L-B1, I14-M12-C5983-V1.5 L-B1, I14-M11-C3696-V1.5 L-B1, I22-M13-C5712-V1.5 L-B1, I22-M14-C2333-V1.5 L-B1, I22-M15-C5664-V1.5 L-B1, I22-M16-C5696-V1.5 L-B1, I22-M09-C5792-V1.5 L-B1, I22-M10-C70-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I20-M16-C207-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M10-C197-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I14-M16-C6285-V1.5 L-B1, I14-M05-C5978-V1.5 L-B1, I14-M06-C1903-V1.5 L-B1, I14-M15-C1425-V1.5 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M06-C360-V0.5 L-B1, I13-M01-C8479-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I09-MN10C3-C580-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I09-MN10C3-C552-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I21-M09-C3313-V0.7 L-B1, I21-M03-C192-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I13-M04-C2777-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-MN05C3-C6329-V0.5 L-B1, I22-MN16C2-C5935-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M14-C480-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M14-C408-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M15-C139-V0.7 L-B1, I21-M01-C144-V0.7 L-B1, I21-M02-C72-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M14-C1392-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M14-C4256-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-MN13C1-C1296-V0.5 L-B1, I22-MN12C3-C7948-V0.5 L-B1, I22-MN12C2-C5754-V0.5 L-B1, I22-MN12C1-C883-V0.5 L-B1, I22-MN11C4-C1080-V0.5 L-B1, I10-MN09C2-C9566-V0.5 L-B1, I10-MN10C2-C10190-V0.5 L-B1, I10-MN10C3-C289-V0.5 L-B1, I10-MN08C1-C5026-V0.5 L-B1, I10-MN10C1-C4966-V0.5 L-B1, I10-MN08C2-C1518-V0.5 L-B1, I10-MN09C3-C4896-V0.5 L-B1, I22-MN04C3-C6840-V0.5 L-B1, I22-MN04C4-C6639-V0.5 L-B1, I22-MN05C2-C6737-V0.5 L-B1, I22-MN06C4-C5163-V0.5 L-B1, I22-MN15C1-C910-V0.5 L-B1, I22-MN18C1-C1867-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-MN13C4-C168-V0.5 L-B1, I22-MN12C4-C216-V0.5 L-B1, I22-MN12C3-C192-V0.5 L-B1, I22-MN16C4-C456-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-MN16C2-C3480-V0.5 L-B1, I22-MN13C4-C1944-V0.5 L-B1, I22-MN12C4-C768-V0.5 L-B1, I22-MN12C3-C2568-V0.5 L-B1, I22-MN15C1-C8520-V0.5 L-B1, I22-MN14C4-C8520-V0.5 L-B1, I22-MN13C1-C5112-V0.5 L-B1, I22-MN14C3-C1080-V0.5 L-B1, I10-MN11C2-C24-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-MN16C3-C1184-V0.5 L-B1, I22-MN12C4-C120-V0.5 L-B1, I22-MN15C1-C288-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M13-C1080-V0.5 L-B1, I22-M14-C327-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M13-C1224-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M13-C1194-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M13-C1059-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M13-C1387-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M13-C1495-V0.7 L-B1</t>
+  </si>
+  <si>
+    <t>I09-MN20C2-C265-V0.5 L-B1, I09-MN19C3-C1089-V0.5 L-B1, I09-MN20C3-C2880-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I09-MN10C3-C2726-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I09-MN06C3-C712-V0.5 L-B1, I09-MN10C3-C7034-V0.5 L-B1</t>
+  </si>
+  <si>
     <t>I22-M04-C12-V0.5 L-B1, I22-M01-C2-V0.5 L-B1, I22-M16-C137-V0.5 L-B1</t>
   </si>
   <si>
+    <t>I09-MN06C3-C709-V0.5 L-B1, I09-MN09C3-C694-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-M01-C4-V0.5 L-B1, I10-MN20C2-C4387-V0.5 L-B1, I22-M16-C658-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I09-MN02C1-C772-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I09-MN03C1-C684-V0.5 L-B1, I09-MN05C2-C96-V0.5 L-B1, I09-MN05C3-C120-V0.5 L-B1, I09-MN04C3-C8424-V0.5 L-B1, I09-MN04C1-C2364-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>I22-MN05C2-C4312-V0.5 L-B1, I22-MN04C4-C3816-V0.5 L-B1, I22-MN05C1-C2-V0.5 L-B1</t>
+  </si>
+  <si>
+    <t>1 | 1.5 L</t>
+  </si>
+  <si>
+    <t>50 | 0.143 L</t>
+  </si>
+  <si>
+    <t>1 | 2.5 L</t>
+  </si>
+  <si>
+    <t>1 | 0.6 L</t>
+  </si>
+  <si>
     <t>1 | 0.5 L</t>
   </si>
   <si>
-    <t>M04D002LI2603-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M02T105L03604-50B-0.143L</t>
-  </si>
-  <si>
-    <t>M02T106L03603-50B-0.143L</t>
-  </si>
-  <si>
-    <t>M02L008L11603-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M02M039L20604-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M02N042LB5601-1B-2.5L</t>
-  </si>
-  <si>
-    <t>M02N042LA5601-1B-2.5L</t>
-  </si>
-  <si>
-    <t>M02N042LC5601-1B-2.5L</t>
-  </si>
-  <si>
-    <t>M02T118LB5601-1B-0.6L</t>
-  </si>
-  <si>
-    <t>M02T114LA5602-1B-0.6L</t>
-  </si>
-  <si>
-    <t>M02T113LA5601-1B-0.6L</t>
-  </si>
-  <si>
-    <t>M02T119LA5601-1B-0.6L</t>
-  </si>
-  <si>
-    <t>M02T118LA5601-1B-0.6L</t>
-  </si>
-  <si>
-    <t>M02Q048L33604-1B-0.6L</t>
-  </si>
-  <si>
-    <t>M02Q047L24606-1B-0.6L</t>
-  </si>
-  <si>
-    <t>M02Q047LA5602-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047L24605-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02M039L20603-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M02L008L11602-1B-1L</t>
-  </si>
-  <si>
-    <t>M02T105L03603-50B-0.143L</t>
-  </si>
-  <si>
-    <t>M02T083LA3601-50B-0.143L</t>
-  </si>
-  <si>
-    <t>M02T083LB4602-50B-0.143L</t>
-  </si>
-  <si>
-    <t>M04D002LF4602-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04B009LA5602-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04B009LA5601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LH2602-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LG2601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M06L004L13601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LF4601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LB4601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04A002LB2601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04L002L14601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LD4601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LM2604-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LI2602-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LI2601-1B-1L</t>
-  </si>
-  <si>
-    <t>M02U043L62601-1B-2.5L</t>
-  </si>
-  <si>
-    <t>M02U043L92601-1B-2.5L</t>
-  </si>
-  <si>
-    <t>M02U043L42601-1B-2.5L</t>
-  </si>
-  <si>
-    <t>M02Q048L33603-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047L14602-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047L24604-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047L24603-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M04L005601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D001LA2601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04L003L33601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04L004601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M0601602-1B-1L</t>
-  </si>
-  <si>
-    <t>M04L002L23602-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02Q047LA5601-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047L24602-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M04D002LM2602-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M04D002LM2602-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04L002L23601-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M04A002LA0602-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M02Q048L33601-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M04D002LH2601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M0601601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04A002LA0601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M04D002LM2601-1B-1.5L</t>
-  </si>
-  <si>
-    <t>M02Q050L01602-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q048L33515-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q048L13504-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M0240501-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02Q050L01526-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02Q053L01506-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047LA5502-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q068L24502-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q068L14501-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q050L01522-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02Q053L01504-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q068L01506-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047L24511-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047LA5501-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M0247518-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047L24510-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02M022L02503-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02M040L33502-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02M040L13501-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02M040L23501-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02M078L02503-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02M110L03502-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02Q053L01503-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q048501-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q048L33511-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02M109L03502-1B-0.7L</t>
-  </si>
-  <si>
-    <t>M02Q047L24508-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q048L33510-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02M039L20505-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02M022L02502-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q050L01521-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M0247516-1B-0.5L</t>
-  </si>
-  <si>
-    <t>M02Q047L24507-1B-0.5L</t>
-  </si>
-  <si>
-    <t>Avellano</t>
-  </si>
-  <si>
-    <t>Cerezo</t>
-  </si>
-  <si>
-    <t>04D002LI2</t>
-  </si>
-  <si>
-    <t>02T105L03</t>
-  </si>
-  <si>
-    <t>02T106L03</t>
-  </si>
-  <si>
-    <t>02L008L11</t>
-  </si>
-  <si>
-    <t>02M039L20</t>
-  </si>
-  <si>
-    <t>02N042LB5</t>
-  </si>
-  <si>
-    <t>02N042LA5</t>
-  </si>
-  <si>
-    <t>02N042LC5</t>
-  </si>
-  <si>
-    <t>02T118LB5</t>
-  </si>
-  <si>
-    <t>02T114LA5</t>
-  </si>
-  <si>
-    <t>02T113LA5</t>
-  </si>
-  <si>
-    <t>02T119LA5</t>
-  </si>
-  <si>
-    <t>02T118LA5</t>
-  </si>
-  <si>
-    <t>02Q048L33</t>
-  </si>
-  <si>
-    <t>02Q047L24</t>
-  </si>
-  <si>
-    <t>02Q047LA5</t>
-  </si>
-  <si>
-    <t>02T083LA3</t>
-  </si>
-  <si>
-    <t>02T083LB4</t>
-  </si>
-  <si>
-    <t>04D002LF4</t>
-  </si>
-  <si>
-    <t>04B009LA5</t>
-  </si>
-  <si>
-    <t>04D002LH2</t>
-  </si>
-  <si>
-    <t>04D002LG2</t>
-  </si>
-  <si>
-    <t>06L004L13</t>
-  </si>
-  <si>
-    <t>04D002LB4</t>
-  </si>
-  <si>
-    <t>04A002LB2</t>
-  </si>
-  <si>
-    <t>04L002L14</t>
-  </si>
-  <si>
-    <t>04D002LD4</t>
-  </si>
-  <si>
-    <t>04D002LM2</t>
-  </si>
-  <si>
-    <t>02U043L62</t>
-  </si>
-  <si>
-    <t>02U043L92</t>
-  </si>
-  <si>
-    <t>02U043L42</t>
-  </si>
-  <si>
-    <t>02Q047L14</t>
-  </si>
-  <si>
-    <t>04L005</t>
-  </si>
-  <si>
-    <t>04D001LA2</t>
-  </si>
-  <si>
-    <t>04L003L33</t>
-  </si>
-  <si>
-    <t>04L004</t>
-  </si>
-  <si>
-    <t>0601</t>
-  </si>
-  <si>
-    <t>04L002L23</t>
-  </si>
-  <si>
-    <t>04A002LA0</t>
-  </si>
-  <si>
-    <t>02Q050L01</t>
-  </si>
-  <si>
-    <t>02Q048L13</t>
-  </si>
-  <si>
-    <t>0240</t>
-  </si>
-  <si>
-    <t>02Q053L01</t>
-  </si>
-  <si>
-    <t>02Q068L24</t>
-  </si>
-  <si>
-    <t>02Q068L14</t>
-  </si>
-  <si>
-    <t>02Q068L01</t>
-  </si>
-  <si>
-    <t>0247</t>
-  </si>
-  <si>
-    <t>02M022L02</t>
-  </si>
-  <si>
-    <t>02M040L33</t>
-  </si>
-  <si>
-    <t>02M040L13</t>
-  </si>
-  <si>
-    <t>02M040L23</t>
-  </si>
-  <si>
-    <t>02M078L02</t>
-  </si>
-  <si>
-    <t>02M110L03</t>
-  </si>
-  <si>
-    <t>02Q048</t>
-  </si>
-  <si>
-    <t>02M109L03</t>
-  </si>
-  <si>
-    <t>1.5 L</t>
-  </si>
-  <si>
-    <t>0.143 L</t>
-  </si>
-  <si>
-    <t>2.5 L</t>
-  </si>
-  <si>
-    <t>0.6 L</t>
-  </si>
-  <si>
-    <t>1 L</t>
-  </si>
-  <si>
-    <t>0.7 L</t>
-  </si>
-  <si>
-    <t>I22-M10-C950</t>
-  </si>
-  <si>
-    <t>I13-M05-C14835</t>
-  </si>
-  <si>
-    <t>I13-M05-C920</t>
-  </si>
-  <si>
-    <t>I10-M04-C3000</t>
-  </si>
-  <si>
-    <t>I10-M02-C512, I10-M03-C6272, I10-M04-C763</t>
-  </si>
-  <si>
-    <t>I12-M06-C656</t>
-  </si>
-  <si>
-    <t>I12-M06-C848</t>
-  </si>
-  <si>
-    <t>I12-M06-C2168</t>
-  </si>
-  <si>
-    <t>I21-M07-C92</t>
-  </si>
-  <si>
-    <t>I21-M07-C204</t>
-  </si>
-  <si>
-    <t>I21-M07-C52</t>
-  </si>
-  <si>
-    <t>I21-M07-C64</t>
-  </si>
-  <si>
-    <t>I21-M07-C56</t>
-  </si>
-  <si>
-    <t>I12-M08-C6840, I21-M07-C1680, I12-M07-C8760, I21-M08-C1128</t>
-  </si>
-  <si>
-    <t>I12-M12-C5640, I12-M08-C2016</t>
-  </si>
-  <si>
-    <t>I10-M05-C960</t>
-  </si>
-  <si>
-    <t>I12-M09-C9120, I12-M10-C9120, I12-M11-C9120, I12-M12-C3480</t>
-  </si>
-  <si>
-    <t>I10-M01-C6272, I10-M02-C5728</t>
-  </si>
-  <si>
-    <t>I21-M07-C620</t>
-  </si>
-  <si>
-    <t>I21-M07-C750</t>
-  </si>
-  <si>
-    <t>I21-M07-C3318</t>
-  </si>
-  <si>
-    <t>I21-M07-C2836</t>
-  </si>
-  <si>
-    <t>I22-M10-C341</t>
-  </si>
-  <si>
-    <t>I22-M10-C1039</t>
-  </si>
-  <si>
-    <t>I22-M10-C690</t>
-  </si>
-  <si>
-    <t>I22-M11-C576, I22-M10-C647</t>
-  </si>
-  <si>
-    <t>I22-M11-C700</t>
-  </si>
-  <si>
-    <t>I20-M15-C2564, I20-M14-C1352</t>
-  </si>
-  <si>
-    <t>I22-M11-C2788</t>
-  </si>
-  <si>
-    <t>I22-M11-C115</t>
-  </si>
-  <si>
-    <t>I22-M11-C345</t>
-  </si>
-  <si>
-    <t>I22-M12-C53</t>
-  </si>
-  <si>
-    <t>I22-M12-C3488, I22-M11-C907</t>
-  </si>
-  <si>
-    <t>I22-M12-C360</t>
-  </si>
-  <si>
-    <t>I14-M11-C1200, I14-M10-C2128, I22-M12-C959</t>
-  </si>
-  <si>
-    <t>I14-M10-C500</t>
-  </si>
-  <si>
-    <t>I12-M05-C1523</t>
-  </si>
-  <si>
-    <t>I12-M05-C790</t>
-  </si>
-  <si>
-    <t>I12-M05-C1424</t>
-  </si>
-  <si>
-    <t>I21-M12-C5180, I21-M05-C8310, I21-M06-C8354, I21-M07-C2026</t>
-  </si>
-  <si>
-    <t>I21-M12-C349</t>
-  </si>
-  <si>
-    <t>I11-M11-C4920, I11-M12-C9120, I21-M10-C8318, I21-M11-C8256, I21-M12-C949, I21-M09-C8364</t>
-  </si>
-  <si>
-    <t>I10-M05-C7800, I11-M07-C2160, I10-M09-C8880, I10-M10-C8880, I10-M11-C8880, I10-M12-C8520, I11-M09-C9120, I11-M10-C9072, I11-M11-C4176</t>
-  </si>
-  <si>
-    <t>I14-M10-C1068</t>
-  </si>
-  <si>
-    <t>I14-M09-C2816, I14-M10-C2627</t>
-  </si>
-  <si>
-    <t>I14-M09-C223</t>
-  </si>
-  <si>
-    <t>I14-M09-C3108</t>
-  </si>
-  <si>
-    <t>I20-M16-C1856, I20-M15-C3011</t>
-  </si>
-  <si>
-    <t>I22-M10-C5680, I22-M09-C5648, I22-M08-C4864</t>
-  </si>
-  <si>
-    <t>I22-MN17C4-C878</t>
-  </si>
-  <si>
-    <t>I10-MN07C3-C1304, I10-MN09C1-C10075, I22-MN16C3-C3123, I22-MN15C1-C5387, I22-MN06C1-C501, I22-MN05C4-C6504, I22-MN10C2-C4308, I22-MN12C1-C6861, I22-MN12C4-C7728, I22-MN13C1-C91, I22-MN13C4-C7633, I22-MN17C4-C5064, I22-MN18C1-C162, I22-MN20C2-C6012, I22-MN20C4-C753</t>
-  </si>
-  <si>
-    <t>I22-M08-C736, I22-M12-C680</t>
-  </si>
-  <si>
-    <t>I22-M14-C795</t>
-  </si>
-  <si>
-    <t>I22-M11-C5717, I22-M12-C5712, I22-M14-C2176</t>
-  </si>
-  <si>
-    <t>I22-M14-C300</t>
-  </si>
-  <si>
-    <t>I10-MN20C1-C2040, I10-MN20C2-C864, I10-MN20C3-C10224</t>
-  </si>
-  <si>
-    <t>I14-M15-C4352, I14-M06-C3920, I14-M07-C5851, I14-M08-C5793, I14-M12-C5983, I14-M11-C3696, I22-M13-C5712, I22-M14-C2333, I22-M15-C5664, I22-M16-C5696, I22-M09-C5792, I22-M10-C70</t>
-  </si>
-  <si>
-    <t>I20-M16-C207</t>
-  </si>
-  <si>
-    <t>I22-M10-C197</t>
-  </si>
-  <si>
-    <t>I14-M16-C6285, I14-M05-C5978, I14-M06-C1903, I14-M15-C1425</t>
-  </si>
-  <si>
-    <t>I21-M06-C360, I21-M01-C360, I13-M03-C412, I13-M01-C9106</t>
-  </si>
-  <si>
-    <t>I09-MN10C3-C580</t>
-  </si>
-  <si>
-    <t>I09-MN10C3-C552</t>
-  </si>
-  <si>
-    <t>I21-M09-C3313, I21-M03-C192</t>
-  </si>
-  <si>
-    <t>I13-M04-C2777</t>
-  </si>
-  <si>
-    <t>I09-MN14C3-C10224, I09-MN14C2-C2184</t>
-  </si>
-  <si>
-    <t>I22-MN05C3-C6329, I22-MN16C2-C5935</t>
-  </si>
-  <si>
-    <t>I22-M14-C480</t>
-  </si>
-  <si>
-    <t>I22-M14-C408</t>
-  </si>
-  <si>
-    <t>I22-M15-C139, I21-M01-C837, I21-M02-C765</t>
-  </si>
-  <si>
-    <t>I22-M14-C1392</t>
-  </si>
-  <si>
-    <t>I22-M14-C4256</t>
-  </si>
-  <si>
-    <t>I22-MN13C1-C1296, I22-MN12C3-C7948, I22-MN12C2-C5754, I22-MN12C1-C883, I22-MN11C4-C1080, I10-MN09C2-C9566, I10-MN10C2-C10190, I10-MN10C3-C289, I10-MN08C1-C5026, I10-MN10C1-C4966, I10-MN08C2-C1518, I10-MN09C3-C4896, I22-MN04C3-C6840, I22-MN04C4-C6639, I22-MN05C2-C6737, I22-MN06C4-C5163, I22-MN15C1-C910, I22-MN18C1-C1867</t>
-  </si>
-  <si>
-    <t>I22-MN13C4-C168, I22-MN12C4-C216, I22-MN12C3-C192, I22-MN16C4-C456</t>
-  </si>
-  <si>
-    <t>I22-MN16C2-C3480, I22-MN13C4-C1944, I22-MN12C4-C768, I22-MN12C3-C2568, I22-MN15C1-C8520, I22-MN14C4-C8520, I22-MN13C1-C5112, I22-MN14C3-C1080, I10-MN11C2-C24</t>
-  </si>
-  <si>
-    <t>I22-MN16C3-C1184, I22-MN12C4-C120, I22-MN15C1-C288</t>
-  </si>
-  <si>
-    <t>I22-M13-C1080, I22-M14-C327</t>
-  </si>
-  <si>
-    <t>I22-M13-C1224</t>
-  </si>
-  <si>
-    <t>I22-M13-C1194</t>
-  </si>
-  <si>
-    <t>I22-M13-C1059</t>
-  </si>
-  <si>
-    <t>I22-M13-C1387</t>
-  </si>
-  <si>
-    <t>I22-M13-C1495</t>
-  </si>
-  <si>
-    <t>I09-MN20C2-C265, I09-MN19C3-C1089, I09-MN20C3-C2880</t>
-  </si>
-  <si>
-    <t>I09-MN10C3-C2726</t>
-  </si>
-  <si>
-    <t>I09-MN06C3-C712, I09-MN10C3-C7034</t>
-  </si>
-  <si>
-    <t>I22-M13-C912, I22-M01-C58, I22-M16-C2894</t>
-  </si>
-  <si>
-    <t>I09-MN06C3-C709, I09-MN09C3-C694</t>
-  </si>
-  <si>
-    <t>I22-M01-C4, I10-MN20C2-C4387, I22-M16-C658</t>
-  </si>
-  <si>
-    <t>I09-MN02C1-C772</t>
-  </si>
-  <si>
-    <t>I09-MN03C1-C684, I09-MN05C2-C96, I09-MN05C3-C120, I09-MN04C3-C8424, I09-MN04C1-C2364</t>
-  </si>
-  <si>
-    <t>I22-MN05C2-C4312, I22-MN04C4-C3816, I22-MN05C1-C2</t>
-  </si>
-  <si>
-    <t>I22-M01-C2, I22-M16-C17, I22-MN20C1-C375</t>
-  </si>
-  <si>
-    <t>I22-M01-C3, I22-MN20C4-C735, I22-M16-C45</t>
-  </si>
-  <si>
-    <t>I22-M10-C950-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I13-M05-C14835-V0.143 L-B50</t>
-  </si>
-  <si>
-    <t>I13-M05-C920-V0.143 L-B50</t>
-  </si>
-  <si>
-    <t>I10-M04-C3000-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I10-M02-C512-V1.5 L-B1, I10-M03-C6272-V1.5 L-B1, I10-M04-C763-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M06-C656-V2.5 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M06-C848-V2.5 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M06-C2168-V2.5 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M07-C92-V0.6 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M07-C204-V0.6 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M07-C52-V0.6 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M07-C64-V0.6 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M07-C56-V0.6 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M08-C6840-V0.6 L-B1, I21-M07-C1680-V0.6 L-B1, I12-M07-C8760-V0.6 L-B1, I21-M08-C1128-V0.6 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M12-C5640-V0.6 L-B1, I12-M08-C2016-V0.6 L-B1</t>
-  </si>
-  <si>
-    <t>I10-M05-C960-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M09-C9120-V0.5 L-B1, I12-M10-C9120-V0.5 L-B1, I12-M11-C9120-V0.5 L-B1, I12-M12-C3480-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I10-M01-C6272-V1.5 L-B1, I10-M02-C5728-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M07-C620-V1 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M07-C750-V0.143 L-B50</t>
-  </si>
-  <si>
-    <t>I21-M07-C3318-V0.143 L-B50</t>
-  </si>
-  <si>
-    <t>I21-M07-C2836-V0.143 L-B50</t>
-  </si>
-  <si>
-    <t>I22-M10-C341-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M10-C1039-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M10-C690-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M11-C576-V1.5 L-B1, I22-M10-C647-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M11-C700-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I20-M15-C2564-V1.5 L-B1, I20-M14-C1352-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M11-C2788-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M11-C115-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M11-C345-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M12-C53-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M12-C3488-V1.5 L-B1, I22-M11-C907-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M12-C360-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I14-M11-C1200-V1.5 L-B1, I14-M10-C2128-V1.5 L-B1, I22-M12-C959-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I14-M10-C500-V1 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M05-C1523-V2.5 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M05-C790-V2.5 L-B1</t>
-  </si>
-  <si>
-    <t>I12-M05-C1424-V2.5 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M12-C5180-V0.5 L-B1, I21-M05-C8310-V0.5 L-B1, I21-M06-C8354-V0.5 L-B1, I21-M07-C2026-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M12-C349-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I11-M11-C4920-V0.5 L-B1, I11-M12-C9120-V0.5 L-B1, I21-M10-C8318-V0.5 L-B1, I21-M11-C8256-V0.5 L-B1, I21-M12-C949-V0.5 L-B1, I21-M09-C8364-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I10-M05-C7800-V0.5 L-B1, I11-M07-C2160-V0.5 L-B1, I10-M09-C8880-V0.5 L-B1, I10-M10-C8880-V0.5 L-B1, I10-M11-C8880-V0.5 L-B1, I10-M12-C8520-V0.5 L-B1, I11-M09-C9120-V0.5 L-B1, I11-M10-C9072-V0.5 L-B1, I11-M11-C4176-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I14-M10-C1068-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I14-M09-C2816-V1.5 L-B1, I14-M10-C2627-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I14-M09-C223-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I14-M09-C3108-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I20-M16-C1856-V1 L-B1, I20-M15-C3011-V1 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M10-C5680-V0.7 L-B1, I22-M09-C5648-V0.7 L-B1, I22-M08-C4864-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I22-MN17C4-C878-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I10-MN07C3-C1304-V0.5 L-B1, I10-MN09C1-C10075-V0.5 L-B1, I22-MN16C3-C3123-V0.5 L-B1, I22-MN15C1-C5387-V0.5 L-B1, I22-MN06C1-C501-V0.5 L-B1, I22-MN05C4-C6504-V0.5 L-B1, I22-MN10C2-C4308-V0.5 L-B1, I22-MN12C1-C6861-V0.5 L-B1, I22-MN12C4-C7728-V0.5 L-B1, I22-MN13C1-C91-V0.5 L-B1, I22-MN13C4-C7633-V0.5 L-B1, I22-MN17C4-C5064-V0.5 L-B1, I22-MN18C1-C162-V0.5 L-B1, I22-MN20C2-C6012-V0.5 L-B1, I22-MN20C4-C753-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M08-C736-V0.7 L-B1, I22-M12-C680-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M14-C795-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M11-C5717-V0.7 L-B1, I22-M12-C5712-V0.7 L-B1, I22-M14-C2176-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M14-C300-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I10-MN20C1-C2040-V0.5 L-B1, I10-MN20C2-C864-V0.5 L-B1, I10-MN20C3-C10224-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I14-M15-C4352-V1.5 L-B1, I14-M06-C3920-V1.5 L-B1, I14-M07-C5851-V1.5 L-B1, I14-M08-C5793-V1.5 L-B1, I14-M12-C5983-V1.5 L-B1, I14-M11-C3696-V1.5 L-B1, I22-M13-C5712-V1.5 L-B1, I22-M14-C2333-V1.5 L-B1, I22-M15-C5664-V1.5 L-B1, I22-M16-C5696-V1.5 L-B1, I22-M09-C5792-V1.5 L-B1, I22-M10-C70-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I20-M16-C207-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M10-C197-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I14-M16-C6285-V1.5 L-B1, I14-M05-C5978-V1.5 L-B1, I14-M06-C1903-V1.5 L-B1, I14-M15-C1425-V1.5 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M06-C360-V0.5 L-B1, I21-M01-C360-V0.5 L-B1, I13-M03-C412-V0.5 L-B1, I13-M01-C9106-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN10C3-C580-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN10C3-C552-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I21-M09-C3313-V0.7 L-B1, I21-M03-C192-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I13-M04-C2777-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN14C3-C10224-V0.5 L-B1, I09-MN14C2-C2184-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-MN05C3-C6329-V0.5 L-B1, I22-MN16C2-C5935-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M14-C480-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M14-C408-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M15-C139-V0.7 L-B1, I21-M01-C837-V0.7 L-B1, I21-M02-C765-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M14-C1392-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M14-C4256-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-MN13C1-C1296-V0.5 L-B1, I22-MN12C3-C7948-V0.5 L-B1, I22-MN12C2-C5754-V0.5 L-B1, I22-MN12C1-C883-V0.5 L-B1, I22-MN11C4-C1080-V0.5 L-B1, I10-MN09C2-C9566-V0.5 L-B1, I10-MN10C2-C10190-V0.5 L-B1, I10-MN10C3-C289-V0.5 L-B1, I10-MN08C1-C5026-V0.5 L-B1, I10-MN10C1-C4966-V0.5 L-B1, I10-MN08C2-C1518-V0.5 L-B1, I10-MN09C3-C4896-V0.5 L-B1, I22-MN04C3-C6840-V0.5 L-B1, I22-MN04C4-C6639-V0.5 L-B1, I22-MN05C2-C6737-V0.5 L-B1, I22-MN06C4-C5163-V0.5 L-B1, I22-MN15C1-C910-V0.5 L-B1, I22-MN18C1-C1867-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-MN13C4-C168-V0.5 L-B1, I22-MN12C4-C216-V0.5 L-B1, I22-MN12C3-C192-V0.5 L-B1, I22-MN16C4-C456-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-MN16C2-C3480-V0.5 L-B1, I22-MN13C4-C1944-V0.5 L-B1, I22-MN12C4-C768-V0.5 L-B1, I22-MN12C3-C2568-V0.5 L-B1, I22-MN15C1-C8520-V0.5 L-B1, I22-MN14C4-C8520-V0.5 L-B1, I22-MN13C1-C5112-V0.5 L-B1, I22-MN14C3-C1080-V0.5 L-B1, I10-MN11C2-C24-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-MN16C3-C1184-V0.5 L-B1, I22-MN12C4-C120-V0.5 L-B1, I22-MN15C1-C288-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M13-C1080-V0.5 L-B1, I22-M14-C327-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M13-C1224-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M13-C1194-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M13-C1059-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M13-C1387-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M13-C1495-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN20C2-C265-V0.5 L-B1, I09-MN19C3-C1089-V0.5 L-B1, I09-MN20C3-C2880-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN10C3-C2726-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN06C3-C712-V0.5 L-B1, I09-MN10C3-C7034-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M13-C912-V0.7 L-B1, I22-M01-C58-V0.7 L-B1, I22-M16-C2894-V0.7 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN06C3-C709-V0.5 L-B1, I09-MN09C3-C694-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M01-C4-V0.5 L-B1, I10-MN20C2-C4387-V0.5 L-B1, I22-M16-C658-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN02C1-C772-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I09-MN03C1-C684-V0.5 L-B1, I09-MN05C2-C96-V0.5 L-B1, I09-MN05C3-C120-V0.5 L-B1, I09-MN04C3-C8424-V0.5 L-B1, I09-MN04C1-C2364-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-MN05C2-C4312-V0.5 L-B1, I22-MN04C4-C3816-V0.5 L-B1, I22-MN05C1-C2-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M01-C2-V0.5 L-B1, I22-M16-C17-V0.5 L-B1, I22-MN20C1-C375-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>I22-M01-C3-V0.5 L-B1, I22-MN20C4-C735-V0.5 L-B1, I22-M16-C45-V0.5 L-B1</t>
-  </si>
-  <si>
-    <t>1 | 1.5 L</t>
-  </si>
-  <si>
-    <t>50 | 0.143 L</t>
-  </si>
-  <si>
-    <t>1 | 2.5 L</t>
-  </si>
-  <si>
-    <t>1 | 0.6 L</t>
-  </si>
-  <si>
     <t>1 | 1 L</t>
-  </si>
-  <si>
-    <t>1 | 0.7 L</t>
   </si>
   <si>
     <t>Día de la semana</t>
@@ -1591,13 +1507,13 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
       <c r="C2" s="1">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="D2" t="s">
         <v>24</v>
@@ -1621,16 +1537,16 @@
         <v>46027</v>
       </c>
       <c r="K2" s="1">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="L2" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="M2" t="s">
         <v>11</v>
       </c>
       <c r="N2" s="1">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="O2" t="s">
         <v>29</v>
@@ -1642,10 +1558,10 @@
         <v>30</v>
       </c>
       <c r="R2">
-        <v>151</v>
+        <v>3864</v>
       </c>
       <c r="S2">
-        <v>151</v>
+        <v>3864</v>
       </c>
       <c r="T2" t="s">
         <v>31</v>
@@ -1654,7 +1570,7 @@
         <v>32</v>
       </c>
       <c r="V2">
-        <v>151</v>
+        <v>3864</v>
       </c>
       <c r="W2" t="s">
         <v>33</v>
@@ -1667,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1752,10 +1668,10 @@
         <v>46132</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F2" t="s">
         <v>26</v>
@@ -1791,7 +1707,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R2">
         <v>950</v>
@@ -1800,16 +1716,16 @@
         <v>950</v>
       </c>
       <c r="T2" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="U2" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="V2">
         <v>950</v>
       </c>
       <c r="W2" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1826,7 +1742,7 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s">
         <v>26</v>
@@ -1862,7 +1778,7 @@
         <v>50</v>
       </c>
       <c r="Q3" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="R3">
         <v>14835</v>
@@ -1871,16 +1787,16 @@
         <v>14835</v>
       </c>
       <c r="T3" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="U3" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="V3">
         <v>14835</v>
       </c>
       <c r="W3" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="4" spans="1:23">
@@ -1897,7 +1813,7 @@
         <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F4" t="s">
         <v>26</v>
@@ -1933,7 +1849,7 @@
         <v>50</v>
       </c>
       <c r="Q4" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="R4">
         <v>920</v>
@@ -1942,16 +1858,16 @@
         <v>920</v>
       </c>
       <c r="T4" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="U4" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="V4">
         <v>920</v>
       </c>
       <c r="W4" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -1968,7 +1884,7 @@
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
         <v>26</v>
@@ -2004,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R5">
         <v>3000</v>
@@ -2013,16 +1929,16 @@
         <v>3000</v>
       </c>
       <c r="T5" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="U5" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="V5">
         <v>3000</v>
       </c>
       <c r="W5" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -2039,7 +1955,7 @@
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F6" t="s">
         <v>26</v>
@@ -2075,7 +1991,7 @@
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R6">
         <v>7547</v>
@@ -2084,16 +2000,16 @@
         <v>7547</v>
       </c>
       <c r="T6" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="U6" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="V6">
         <v>7547</v>
       </c>
       <c r="W6" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:23">
@@ -2110,7 +2026,7 @@
         <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F7" t="s">
         <v>26</v>
@@ -2146,7 +2062,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="R7">
         <v>656</v>
@@ -2155,16 +2071,16 @@
         <v>656</v>
       </c>
       <c r="T7" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
       <c r="U7" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="V7">
         <v>656</v>
       </c>
       <c r="W7" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -2181,7 +2097,7 @@
         <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="F8" t="s">
         <v>26</v>
@@ -2217,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="R8">
         <v>848</v>
@@ -2226,16 +2142,16 @@
         <v>848</v>
       </c>
       <c r="T8" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="U8" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="V8">
         <v>848</v>
       </c>
       <c r="W8" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -2252,7 +2168,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F9" t="s">
         <v>26</v>
@@ -2288,7 +2204,7 @@
         <v>1</v>
       </c>
       <c r="Q9" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="R9">
         <v>2168</v>
@@ -2297,16 +2213,16 @@
         <v>2168</v>
       </c>
       <c r="T9" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="U9" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="V9">
         <v>2168</v>
       </c>
       <c r="W9" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -2323,7 +2239,7 @@
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="F10" t="s">
         <v>26</v>
@@ -2359,7 +2275,7 @@
         <v>1</v>
       </c>
       <c r="Q10" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R10">
         <v>92</v>
@@ -2368,16 +2284,16 @@
         <v>92</v>
       </c>
       <c r="T10" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="U10" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="V10">
         <v>92</v>
       </c>
       <c r="W10" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:23">
@@ -2394,7 +2310,7 @@
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F11" t="s">
         <v>26</v>
@@ -2430,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="Q11" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R11">
         <v>204</v>
@@ -2439,16 +2355,16 @@
         <v>204</v>
       </c>
       <c r="T11" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="U11" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="V11">
         <v>204</v>
       </c>
       <c r="W11" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -2465,7 +2381,7 @@
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
@@ -2501,7 +2417,7 @@
         <v>1</v>
       </c>
       <c r="Q12" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R12">
         <v>52</v>
@@ -2510,16 +2426,16 @@
         <v>52</v>
       </c>
       <c r="T12" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="U12" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="V12">
         <v>52</v>
       </c>
       <c r="W12" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="13" spans="1:23">
@@ -2536,7 +2452,7 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F13" t="s">
         <v>26</v>
@@ -2572,7 +2488,7 @@
         <v>1</v>
       </c>
       <c r="Q13" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R13">
         <v>64</v>
@@ -2581,16 +2497,16 @@
         <v>64</v>
       </c>
       <c r="T13" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="U13" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="V13">
         <v>64</v>
       </c>
       <c r="W13" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -2607,7 +2523,7 @@
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F14" t="s">
         <v>26</v>
@@ -2643,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="Q14" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R14">
         <v>56</v>
@@ -2652,16 +2568,16 @@
         <v>56</v>
       </c>
       <c r="T14" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="U14" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="V14">
         <v>56</v>
       </c>
       <c r="W14" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="15" spans="1:23">
@@ -2678,7 +2594,7 @@
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F15" t="s">
         <v>26</v>
@@ -2714,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="Q15" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R15">
         <v>18408</v>
@@ -2723,16 +2639,16 @@
         <v>18408</v>
       </c>
       <c r="T15" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="U15" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="V15">
         <v>18408</v>
       </c>
       <c r="W15" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -2749,7 +2665,7 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F16" t="s">
         <v>26</v>
@@ -2785,7 +2701,7 @@
         <v>1</v>
       </c>
       <c r="Q16" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R16">
         <v>7656</v>
@@ -2794,16 +2710,16 @@
         <v>7656</v>
       </c>
       <c r="T16" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="U16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="V16">
         <v>7656</v>
       </c>
       <c r="W16" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2820,7 +2736,7 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F17" t="s">
         <v>26</v>
@@ -2856,7 +2772,7 @@
         <v>1</v>
       </c>
       <c r="Q17" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R17">
         <v>960</v>
@@ -2865,16 +2781,16 @@
         <v>960</v>
       </c>
       <c r="T17" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="U17" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="V17">
         <v>960</v>
       </c>
       <c r="W17" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:23">
@@ -2891,7 +2807,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F18" t="s">
         <v>26</v>
@@ -2927,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="Q18" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R18">
         <v>30840</v>
@@ -2936,16 +2852,16 @@
         <v>30840</v>
       </c>
       <c r="T18" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="U18" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="V18">
         <v>30840</v>
       </c>
       <c r="W18" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -2962,7 +2878,7 @@
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="F19" t="s">
         <v>26</v>
@@ -2998,7 +2914,7 @@
         <v>1</v>
       </c>
       <c r="Q19" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R19">
         <v>12000</v>
@@ -3007,16 +2923,16 @@
         <v>12000</v>
       </c>
       <c r="T19" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="U19" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="V19">
         <v>12000</v>
       </c>
       <c r="W19" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -3033,7 +2949,7 @@
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="F20" t="s">
         <v>26</v>
@@ -3069,7 +2985,7 @@
         <v>1</v>
       </c>
       <c r="Q20" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="R20">
         <v>620</v>
@@ -3078,16 +2994,16 @@
         <v>620</v>
       </c>
       <c r="T20" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="U20" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="V20">
         <v>620</v>
       </c>
       <c r="W20" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -3104,7 +3020,7 @@
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F21" t="s">
         <v>26</v>
@@ -3140,7 +3056,7 @@
         <v>50</v>
       </c>
       <c r="Q21" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="R21">
         <v>750</v>
@@ -3149,16 +3065,16 @@
         <v>750</v>
       </c>
       <c r="T21" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="U21" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="V21">
         <v>750</v>
       </c>
       <c r="W21" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -3175,7 +3091,7 @@
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="F22" t="s">
         <v>26</v>
@@ -3211,7 +3127,7 @@
         <v>50</v>
       </c>
       <c r="Q22" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="R22">
         <v>3318</v>
@@ -3220,16 +3136,16 @@
         <v>3318</v>
       </c>
       <c r="T22" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="U22" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="V22">
         <v>3318</v>
       </c>
       <c r="W22" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -3246,7 +3162,7 @@
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F23" t="s">
         <v>26</v>
@@ -3282,7 +3198,7 @@
         <v>50</v>
       </c>
       <c r="Q23" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="R23">
         <v>2836</v>
@@ -3291,16 +3207,16 @@
         <v>2836</v>
       </c>
       <c r="T23" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="U23" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="V23">
         <v>2836</v>
       </c>
       <c r="W23" t="s">
-        <v>377</v>
+        <v>349</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -3314,10 +3230,10 @@
         <v>46105</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F24" t="s">
         <v>26</v>
@@ -3353,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="Q24" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R24">
         <v>341</v>
@@ -3362,16 +3278,16 @@
         <v>341</v>
       </c>
       <c r="T24" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="U24" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="V24">
         <v>341</v>
       </c>
       <c r="W24" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -3385,10 +3301,10 @@
         <v>46104</v>
       </c>
       <c r="D25" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E25" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F25" t="s">
         <v>26</v>
@@ -3424,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="Q25" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R25">
         <v>1039</v>
@@ -3433,16 +3349,16 @@
         <v>1039</v>
       </c>
       <c r="T25" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="U25" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="V25">
         <v>1039</v>
       </c>
       <c r="W25" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -3456,10 +3372,10 @@
         <v>46104</v>
       </c>
       <c r="D26" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E26" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F26" t="s">
         <v>26</v>
@@ -3495,7 +3411,7 @@
         <v>1</v>
       </c>
       <c r="Q26" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R26">
         <v>690</v>
@@ -3504,16 +3420,16 @@
         <v>690</v>
       </c>
       <c r="T26" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="U26" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="V26">
         <v>690</v>
       </c>
       <c r="W26" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="27" spans="1:23">
@@ -3527,10 +3443,10 @@
         <v>46104</v>
       </c>
       <c r="D27" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E27" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F27" t="s">
         <v>26</v>
@@ -3566,7 +3482,7 @@
         <v>1</v>
       </c>
       <c r="Q27" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R27">
         <v>1223</v>
@@ -3575,16 +3491,16 @@
         <v>1223</v>
       </c>
       <c r="T27" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="U27" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="V27">
         <v>1223</v>
       </c>
       <c r="W27" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:23">
@@ -3598,10 +3514,10 @@
         <v>46104</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F28" t="s">
         <v>26</v>
@@ -3637,7 +3553,7 @@
         <v>1</v>
       </c>
       <c r="Q28" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R28">
         <v>700</v>
@@ -3646,16 +3562,16 @@
         <v>700</v>
       </c>
       <c r="T28" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="U28" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="V28">
         <v>700</v>
       </c>
       <c r="W28" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -3669,10 +3585,10 @@
         <v>46101</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F29" t="s">
         <v>26</v>
@@ -3708,7 +3624,7 @@
         <v>1</v>
       </c>
       <c r="Q29" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R29">
         <v>3916</v>
@@ -3717,16 +3633,16 @@
         <v>3916</v>
       </c>
       <c r="T29" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="U29" t="s">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="V29">
         <v>3916</v>
       </c>
       <c r="W29" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:23">
@@ -3740,10 +3656,10 @@
         <v>46101</v>
       </c>
       <c r="D30" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F30" t="s">
         <v>26</v>
@@ -3779,7 +3695,7 @@
         <v>1</v>
       </c>
       <c r="Q30" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R30">
         <v>2788</v>
@@ -3788,16 +3704,16 @@
         <v>2788</v>
       </c>
       <c r="T30" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="U30" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="V30">
         <v>2788</v>
       </c>
       <c r="W30" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:23">
@@ -3811,10 +3727,10 @@
         <v>46101</v>
       </c>
       <c r="D31" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F31" t="s">
         <v>26</v>
@@ -3850,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="Q31" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R31">
         <v>115</v>
@@ -3859,16 +3775,16 @@
         <v>115</v>
       </c>
       <c r="T31" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="U31" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="V31">
         <v>115</v>
       </c>
       <c r="W31" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="32" spans="1:23">
@@ -3882,10 +3798,10 @@
         <v>46101</v>
       </c>
       <c r="D32" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E32" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="F32" t="s">
         <v>26</v>
@@ -3921,7 +3837,7 @@
         <v>1</v>
       </c>
       <c r="Q32" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R32">
         <v>345</v>
@@ -3930,16 +3846,16 @@
         <v>345</v>
       </c>
       <c r="T32" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="U32" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
       <c r="V32">
         <v>345</v>
       </c>
       <c r="W32" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="33" spans="1:23">
@@ -3953,10 +3869,10 @@
         <v>46100</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E33" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F33" t="s">
         <v>26</v>
@@ -3992,7 +3908,7 @@
         <v>1</v>
       </c>
       <c r="Q33" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R33">
         <v>53</v>
@@ -4001,16 +3917,16 @@
         <v>53</v>
       </c>
       <c r="T33" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="U33" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="V33">
         <v>53</v>
       </c>
       <c r="W33" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" spans="1:23">
@@ -4024,10 +3940,10 @@
         <v>46100</v>
       </c>
       <c r="D34" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E34" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="F34" t="s">
         <v>26</v>
@@ -4063,7 +3979,7 @@
         <v>1</v>
       </c>
       <c r="Q34" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R34">
         <v>4395</v>
@@ -4072,16 +3988,16 @@
         <v>4395</v>
       </c>
       <c r="T34" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="U34" t="s">
-        <v>315</v>
+        <v>295</v>
       </c>
       <c r="V34">
         <v>4395</v>
       </c>
       <c r="W34" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="35" spans="1:23">
@@ -4095,10 +4011,10 @@
         <v>46100</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E35" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F35" t="s">
         <v>26</v>
@@ -4134,7 +4050,7 @@
         <v>1</v>
       </c>
       <c r="Q35" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R35">
         <v>360</v>
@@ -4143,16 +4059,16 @@
         <v>360</v>
       </c>
       <c r="T35" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="U35" t="s">
-        <v>316</v>
+        <v>296</v>
       </c>
       <c r="V35">
         <v>360</v>
       </c>
       <c r="W35" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="36" spans="1:23">
@@ -4166,10 +4082,10 @@
         <v>46099</v>
       </c>
       <c r="D36" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F36" t="s">
         <v>26</v>
@@ -4205,7 +4121,7 @@
         <v>1</v>
       </c>
       <c r="Q36" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R36">
         <v>4287</v>
@@ -4214,16 +4130,16 @@
         <v>4287</v>
       </c>
       <c r="T36" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="U36" t="s">
-        <v>317</v>
+        <v>297</v>
       </c>
       <c r="V36">
         <v>4287</v>
       </c>
       <c r="W36" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="37" spans="1:23">
@@ -4237,10 +4153,10 @@
         <v>46099</v>
       </c>
       <c r="D37" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="F37" t="s">
         <v>26</v>
@@ -4276,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="Q37" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="R37">
         <v>500</v>
@@ -4285,16 +4201,16 @@
         <v>500</v>
       </c>
       <c r="T37" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="U37" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="V37">
         <v>500</v>
       </c>
       <c r="W37" t="s">
-        <v>380</v>
+        <v>353</v>
       </c>
     </row>
     <row r="38" spans="1:23">
@@ -4311,7 +4227,7 @@
         <v>24</v>
       </c>
       <c r="E38" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F38" t="s">
         <v>26</v>
@@ -4347,7 +4263,7 @@
         <v>1</v>
       </c>
       <c r="Q38" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="R38">
         <v>1523</v>
@@ -4356,16 +4272,16 @@
         <v>1523</v>
       </c>
       <c r="T38" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="U38" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="V38">
         <v>1523</v>
       </c>
       <c r="W38" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="39" spans="1:23">
@@ -4382,7 +4298,7 @@
         <v>24</v>
       </c>
       <c r="E39" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F39" t="s">
         <v>26</v>
@@ -4418,7 +4334,7 @@
         <v>1</v>
       </c>
       <c r="Q39" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="R39">
         <v>790</v>
@@ -4427,16 +4343,16 @@
         <v>790</v>
       </c>
       <c r="T39" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="U39" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="V39">
         <v>790</v>
       </c>
       <c r="W39" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="40" spans="1:23">
@@ -4453,7 +4369,7 @@
         <v>24</v>
       </c>
       <c r="E40" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F40" t="s">
         <v>26</v>
@@ -4489,7 +4405,7 @@
         <v>1</v>
       </c>
       <c r="Q40" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="R40">
         <v>1424</v>
@@ -4498,16 +4414,16 @@
         <v>1424</v>
       </c>
       <c r="T40" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="U40" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
       <c r="V40">
         <v>1424</v>
       </c>
       <c r="W40" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="41" spans="1:23">
@@ -4524,7 +4440,7 @@
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F41" t="s">
         <v>26</v>
@@ -4560,7 +4476,7 @@
         <v>1</v>
       </c>
       <c r="Q41" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R41">
         <v>23870</v>
@@ -4569,16 +4485,16 @@
         <v>23870</v>
       </c>
       <c r="T41" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="U41" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="V41">
         <v>23870</v>
       </c>
       <c r="W41" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="42" spans="1:23">
@@ -4595,7 +4511,7 @@
         <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F42" t="s">
         <v>26</v>
@@ -4631,7 +4547,7 @@
         <v>1</v>
       </c>
       <c r="Q42" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R42">
         <v>349</v>
@@ -4640,16 +4556,16 @@
         <v>349</v>
       </c>
       <c r="T42" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="U42" t="s">
-        <v>323</v>
+        <v>303</v>
       </c>
       <c r="V42">
         <v>349</v>
       </c>
       <c r="W42" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="43" spans="1:23">
@@ -4666,7 +4582,7 @@
         <v>24</v>
       </c>
       <c r="E43" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="F43" t="s">
         <v>26</v>
@@ -4702,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="Q43" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R43">
         <v>39927</v>
@@ -4711,33 +4627,33 @@
         <v>39927</v>
       </c>
       <c r="T43" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="U43" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="V43">
         <v>39927</v>
       </c>
       <c r="W43" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" spans="1:23">
       <c r="A44">
-        <v>865</v>
+        <v>834</v>
       </c>
       <c r="B44" t="s">
         <v>76</v>
       </c>
       <c r="C44" s="1">
-        <v>46079</v>
+        <v>46055</v>
       </c>
       <c r="D44" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="E44" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="F44" t="s">
         <v>26</v>
@@ -4749,22 +4665,22 @@
         <v>28</v>
       </c>
       <c r="I44" s="1">
-        <v>46108</v>
+        <v>46085</v>
       </c>
       <c r="J44" s="1">
-        <v>46139</v>
+        <v>46115</v>
       </c>
       <c r="K44" s="1">
-        <v>46199</v>
+        <v>46175</v>
       </c>
       <c r="L44" s="1">
-        <v>46259</v>
+        <v>46234</v>
       </c>
       <c r="M44" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N44" s="1">
-        <v>46139</v>
+        <v>46175</v>
       </c>
       <c r="O44" t="s">
         <v>29</v>
@@ -4773,42 +4689,42 @@
         <v>1</v>
       </c>
       <c r="Q44" t="s">
-        <v>30</v>
+        <v>177</v>
       </c>
       <c r="R44">
-        <v>67488</v>
+        <v>4867</v>
       </c>
       <c r="S44">
-        <v>67488</v>
+        <v>4867</v>
       </c>
       <c r="T44" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="U44" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="V44">
-        <v>67488</v>
+        <v>4867</v>
       </c>
       <c r="W44" t="s">
-        <v>33</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45" spans="1:23">
       <c r="A45">
-        <v>864</v>
+        <v>833</v>
       </c>
       <c r="B45" t="s">
         <v>77</v>
       </c>
       <c r="C45" s="1">
-        <v>46079</v>
+        <v>46055</v>
       </c>
       <c r="D45" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E45" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F45" t="s">
         <v>26</v>
@@ -4820,22 +4736,22 @@
         <v>28</v>
       </c>
       <c r="I45" s="1">
-        <v>46108</v>
+        <v>46085</v>
       </c>
       <c r="J45" s="1">
-        <v>46139</v>
+        <v>46115</v>
       </c>
       <c r="K45" s="1">
-        <v>46199</v>
+        <v>46175</v>
       </c>
       <c r="L45" s="1">
-        <v>46259</v>
+        <v>46234</v>
       </c>
       <c r="M45" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N45" s="1">
-        <v>46139</v>
+        <v>46175</v>
       </c>
       <c r="O45" t="s">
         <v>29</v>
@@ -4844,42 +4760,42 @@
         <v>1</v>
       </c>
       <c r="Q45" t="s">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c r="R45">
-        <v>1068</v>
+        <v>16192</v>
       </c>
       <c r="S45">
-        <v>1068</v>
+        <v>16192</v>
       </c>
       <c r="T45" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="U45" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="V45">
-        <v>1068</v>
+        <v>16192</v>
       </c>
       <c r="W45" t="s">
-        <v>376</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:23">
       <c r="A46">
-        <v>863</v>
+        <v>830</v>
       </c>
       <c r="B46" t="s">
         <v>78</v>
       </c>
       <c r="C46" s="1">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="D46" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>162</v>
+        <v>136</v>
       </c>
       <c r="F46" t="s">
         <v>26</v>
@@ -4891,22 +4807,22 @@
         <v>28</v>
       </c>
       <c r="I46" s="1">
-        <v>46108</v>
+        <v>46080</v>
       </c>
       <c r="J46" s="1">
-        <v>46139</v>
+        <v>46111</v>
       </c>
       <c r="K46" s="1">
-        <v>46198</v>
+        <v>46170</v>
       </c>
       <c r="L46" s="1">
-        <v>46258</v>
+        <v>46230</v>
       </c>
       <c r="M46" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N46" s="1">
-        <v>46139</v>
+        <v>46170</v>
       </c>
       <c r="O46" t="s">
         <v>29</v>
@@ -4915,42 +4831,42 @@
         <v>1</v>
       </c>
       <c r="Q46" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="R46">
-        <v>5443</v>
+        <v>878</v>
       </c>
       <c r="S46">
-        <v>5443</v>
+        <v>4</v>
       </c>
       <c r="T46" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="U46" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="V46">
-        <v>5443</v>
+        <v>878</v>
       </c>
       <c r="W46" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="47" spans="1:23">
       <c r="A47">
-        <v>862</v>
+        <v>829</v>
       </c>
       <c r="B47" t="s">
         <v>79</v>
       </c>
       <c r="C47" s="1">
-        <v>46078</v>
+        <v>46050</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="E47" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="F47" t="s">
         <v>26</v>
@@ -4962,22 +4878,22 @@
         <v>28</v>
       </c>
       <c r="I47" s="1">
-        <v>46108</v>
+        <v>46080</v>
       </c>
       <c r="J47" s="1">
-        <v>46139</v>
+        <v>46111</v>
       </c>
       <c r="K47" s="1">
-        <v>46198</v>
+        <v>46170</v>
       </c>
       <c r="L47" s="1">
-        <v>46258</v>
+        <v>46230</v>
       </c>
       <c r="M47" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N47" s="1">
-        <v>46139</v>
+        <v>46170</v>
       </c>
       <c r="O47" t="s">
         <v>29</v>
@@ -4986,42 +4902,42 @@
         <v>1</v>
       </c>
       <c r="Q47" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="R47">
+        <v>65506</v>
+      </c>
+      <c r="S47">
+        <v>36</v>
+      </c>
+      <c r="T47" t="s">
         <v>223</v>
       </c>
-      <c r="S47">
-        <v>223</v>
-      </c>
-      <c r="T47" t="s">
-        <v>235</v>
-      </c>
       <c r="U47" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="V47">
-        <v>223</v>
+        <v>65506</v>
       </c>
       <c r="W47" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="1:23">
       <c r="A48">
-        <v>861</v>
+        <v>828</v>
       </c>
       <c r="B48" t="s">
         <v>80</v>
       </c>
       <c r="C48" s="1">
-        <v>46078</v>
+        <v>46051</v>
       </c>
       <c r="D48" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E48" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="F48" t="s">
         <v>26</v>
@@ -5033,22 +4949,22 @@
         <v>28</v>
       </c>
       <c r="I48" s="1">
-        <v>46108</v>
+        <v>46080</v>
       </c>
       <c r="J48" s="1">
-        <v>46139</v>
+        <v>46111</v>
       </c>
       <c r="K48" s="1">
-        <v>46198</v>
+        <v>46171</v>
       </c>
       <c r="L48" s="1">
-        <v>46258</v>
+        <v>46231</v>
       </c>
       <c r="M48" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N48" s="1">
-        <v>46139</v>
+        <v>46171</v>
       </c>
       <c r="O48" t="s">
         <v>29</v>
@@ -5057,42 +4973,42 @@
         <v>1</v>
       </c>
       <c r="Q48" t="s">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c r="R48">
-        <v>3108</v>
+        <v>1416</v>
       </c>
       <c r="S48">
-        <v>3108</v>
+        <v>1416</v>
       </c>
       <c r="T48" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="U48" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="V48">
-        <v>3108</v>
+        <v>1416</v>
       </c>
       <c r="W48" t="s">
-        <v>376</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49" spans="1:23">
       <c r="A49">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="B49" t="s">
         <v>81</v>
       </c>
       <c r="C49" s="1">
-        <v>46055</v>
+        <v>46051</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E49" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="F49" t="s">
         <v>26</v>
@@ -5104,22 +5020,22 @@
         <v>28</v>
       </c>
       <c r="I49" s="1">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="J49" s="1">
-        <v>46115</v>
+        <v>46111</v>
       </c>
       <c r="K49" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="L49" s="1">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="M49" t="s">
         <v>10</v>
       </c>
       <c r="N49" s="1">
-        <v>46175</v>
+        <v>46171</v>
       </c>
       <c r="O49" t="s">
         <v>29</v>
@@ -5128,42 +5044,42 @@
         <v>1</v>
       </c>
       <c r="Q49" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="R49">
-        <v>4867</v>
+        <v>795</v>
       </c>
       <c r="S49">
-        <v>4867</v>
+        <v>795</v>
       </c>
       <c r="T49" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="U49" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="V49">
-        <v>4867</v>
+        <v>795</v>
       </c>
       <c r="W49" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:23">
       <c r="A50">
-        <v>833</v>
+        <v>827</v>
       </c>
       <c r="B50" t="s">
         <v>82</v>
       </c>
       <c r="C50" s="1">
-        <v>46055</v>
+        <v>46050</v>
       </c>
       <c r="D50" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E50" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="F50" t="s">
         <v>26</v>
@@ -5175,22 +5091,22 @@
         <v>28</v>
       </c>
       <c r="I50" s="1">
-        <v>46085</v>
+        <v>46080</v>
       </c>
       <c r="J50" s="1">
-        <v>46115</v>
+        <v>46111</v>
       </c>
       <c r="K50" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="L50" s="1">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="M50" t="s">
         <v>10</v>
       </c>
       <c r="N50" s="1">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="O50" t="s">
         <v>29</v>
@@ -5199,30 +5115,30 @@
         <v>1</v>
       </c>
       <c r="Q50" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="R50">
-        <v>16192</v>
+        <v>13605</v>
       </c>
       <c r="S50">
-        <v>16192</v>
+        <v>13605</v>
       </c>
       <c r="T50" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="U50" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="V50">
-        <v>16192</v>
+        <v>13605</v>
       </c>
       <c r="W50" t="s">
-        <v>381</v>
+        <v>33</v>
       </c>
     </row>
     <row r="51" spans="1:23">
       <c r="A51">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B51" t="s">
         <v>83</v>
@@ -5231,10 +5147,10 @@
         <v>46050</v>
       </c>
       <c r="D51" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="E51" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F51" t="s">
         <v>26</v>
@@ -5270,42 +5186,42 @@
         <v>1</v>
       </c>
       <c r="Q51" t="s">
-        <v>30</v>
+        <v>172</v>
       </c>
       <c r="R51">
-        <v>878</v>
+        <v>300</v>
       </c>
       <c r="S51">
-        <v>4</v>
+        <v>300</v>
       </c>
       <c r="T51" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="U51" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="V51">
-        <v>878</v>
+        <v>300</v>
       </c>
       <c r="W51" t="s">
-        <v>33</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:23">
       <c r="A52">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="B52" t="s">
         <v>84</v>
       </c>
       <c r="C52" s="1">
-        <v>46050</v>
+        <v>46041</v>
       </c>
       <c r="D52" t="s">
         <v>24</v>
       </c>
       <c r="E52" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="F52" t="s">
         <v>26</v>
@@ -5317,22 +5233,22 @@
         <v>28</v>
       </c>
       <c r="I52" s="1">
-        <v>46080</v>
+        <v>46071</v>
       </c>
       <c r="J52" s="1">
-        <v>46111</v>
+        <v>46101</v>
       </c>
       <c r="K52" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="L52" s="1">
-        <v>46230</v>
+        <v>46220</v>
       </c>
       <c r="M52" t="s">
         <v>10</v>
       </c>
       <c r="N52" s="1">
-        <v>46170</v>
+        <v>46161</v>
       </c>
       <c r="O52" t="s">
         <v>29</v>
@@ -5341,42 +5257,42 @@
         <v>1</v>
       </c>
       <c r="Q52" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R52">
-        <v>65506</v>
+        <v>13128</v>
       </c>
       <c r="S52">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="T52" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="U52" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="V52">
-        <v>65506</v>
+        <v>13128</v>
       </c>
       <c r="W52" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="53" spans="1:23">
       <c r="A53">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="B53" t="s">
         <v>85</v>
       </c>
       <c r="C53" s="1">
-        <v>46051</v>
+        <v>46037</v>
       </c>
       <c r="D53" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E53" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="F53" t="s">
         <v>26</v>
@@ -5388,22 +5304,22 @@
         <v>28</v>
       </c>
       <c r="I53" s="1">
-        <v>46080</v>
+        <v>46066</v>
       </c>
       <c r="J53" s="1">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="K53" s="1">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="L53" s="1">
-        <v>46231</v>
+        <v>46217</v>
       </c>
       <c r="M53" t="s">
         <v>10</v>
       </c>
       <c r="N53" s="1">
-        <v>46171</v>
+        <v>46157</v>
       </c>
       <c r="O53" t="s">
         <v>29</v>
@@ -5412,42 +5328,42 @@
         <v>1</v>
       </c>
       <c r="Q53" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="R53">
-        <v>1416</v>
+        <v>54862</v>
       </c>
       <c r="S53">
-        <v>1416</v>
+        <v>54862</v>
       </c>
       <c r="T53" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="U53" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="V53">
-        <v>1416</v>
+        <v>54862</v>
       </c>
       <c r="W53" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
     </row>
     <row r="54" spans="1:23">
       <c r="A54">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="B54" t="s">
         <v>86</v>
       </c>
       <c r="C54" s="1">
-        <v>46051</v>
+        <v>46036</v>
       </c>
       <c r="D54" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E54" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F54" t="s">
         <v>26</v>
@@ -5459,22 +5375,22 @@
         <v>28</v>
       </c>
       <c r="I54" s="1">
-        <v>46080</v>
+        <v>46066</v>
       </c>
       <c r="J54" s="1">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="K54" s="1">
-        <v>46171</v>
+        <v>46156</v>
       </c>
       <c r="L54" s="1">
-        <v>46231</v>
+        <v>46216</v>
       </c>
       <c r="M54" t="s">
         <v>10</v>
       </c>
       <c r="N54" s="1">
-        <v>46171</v>
+        <v>46156</v>
       </c>
       <c r="O54" t="s">
         <v>29</v>
@@ -5483,42 +5399,42 @@
         <v>1</v>
       </c>
       <c r="Q54" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R54">
-        <v>795</v>
+        <v>207</v>
       </c>
       <c r="S54">
-        <v>795</v>
+        <v>207</v>
       </c>
       <c r="T54" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="U54" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="V54">
-        <v>795</v>
+        <v>207</v>
       </c>
       <c r="W54" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:23">
       <c r="A55">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="B55" t="s">
         <v>87</v>
       </c>
       <c r="C55" s="1">
-        <v>46050</v>
+        <v>46036</v>
       </c>
       <c r="D55" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E55" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F55" t="s">
         <v>26</v>
@@ -5530,22 +5446,22 @@
         <v>28</v>
       </c>
       <c r="I55" s="1">
-        <v>46080</v>
+        <v>46066</v>
       </c>
       <c r="J55" s="1">
-        <v>46111</v>
+        <v>46097</v>
       </c>
       <c r="K55" s="1">
-        <v>46170</v>
+        <v>46156</v>
       </c>
       <c r="L55" s="1">
-        <v>46230</v>
+        <v>46216</v>
       </c>
       <c r="M55" t="s">
         <v>10</v>
       </c>
       <c r="N55" s="1">
-        <v>46170</v>
+        <v>46156</v>
       </c>
       <c r="O55" t="s">
         <v>29</v>
@@ -5554,42 +5470,42 @@
         <v>1</v>
       </c>
       <c r="Q55" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="R55">
-        <v>13605</v>
+        <v>197</v>
       </c>
       <c r="S55">
-        <v>13605</v>
+        <v>197</v>
       </c>
       <c r="T55" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="U55" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
       <c r="V55">
-        <v>13605</v>
+        <v>197</v>
       </c>
       <c r="W55" t="s">
-        <v>381</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="1:23">
       <c r="A56">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="B56" t="s">
         <v>88</v>
       </c>
       <c r="C56" s="1">
-        <v>46050</v>
+        <v>46035</v>
       </c>
       <c r="D56" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E56" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="F56" t="s">
         <v>26</v>
@@ -5601,22 +5517,22 @@
         <v>28</v>
       </c>
       <c r="I56" s="1">
-        <v>46080</v>
+        <v>46065</v>
       </c>
       <c r="J56" s="1">
-        <v>46111</v>
+        <v>46094</v>
       </c>
       <c r="K56" s="1">
-        <v>46170</v>
+        <v>46155</v>
       </c>
       <c r="L56" s="1">
-        <v>46230</v>
+        <v>46216</v>
       </c>
       <c r="M56" t="s">
         <v>10</v>
       </c>
       <c r="N56" s="1">
-        <v>46170</v>
+        <v>46155</v>
       </c>
       <c r="O56" t="s">
         <v>29</v>
@@ -5625,42 +5541,42 @@
         <v>1</v>
       </c>
       <c r="Q56" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="R56">
-        <v>300</v>
+        <v>15591</v>
       </c>
       <c r="S56">
-        <v>300</v>
+        <v>15591</v>
       </c>
       <c r="T56" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="U56" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="V56">
-        <v>300</v>
+        <v>15591</v>
       </c>
       <c r="W56" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57" spans="1:23">
       <c r="A57">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="B57" t="s">
         <v>89</v>
       </c>
       <c r="C57" s="1">
-        <v>46041</v>
+        <v>46030</v>
       </c>
       <c r="D57" t="s">
         <v>24</v>
       </c>
       <c r="E57" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="F57" t="s">
         <v>26</v>
@@ -5672,22 +5588,22 @@
         <v>28</v>
       </c>
       <c r="I57" s="1">
-        <v>46071</v>
+        <v>46059</v>
       </c>
       <c r="J57" s="1">
-        <v>46101</v>
+        <v>46090</v>
       </c>
       <c r="K57" s="1">
-        <v>46161</v>
+        <v>46150</v>
       </c>
       <c r="L57" s="1">
-        <v>46220</v>
+        <v>46210</v>
       </c>
       <c r="M57" t="s">
         <v>10</v>
       </c>
       <c r="N57" s="1">
-        <v>46161</v>
+        <v>46150</v>
       </c>
       <c r="O57" t="s">
         <v>29</v>
@@ -5696,42 +5612,42 @@
         <v>1</v>
       </c>
       <c r="Q57" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R57">
-        <v>13128</v>
+        <v>8839</v>
       </c>
       <c r="S57">
-        <v>6</v>
+        <v>8839</v>
       </c>
       <c r="T57" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="U57" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="V57">
-        <v>13128</v>
+        <v>8839</v>
       </c>
       <c r="W57" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="58" spans="1:23">
       <c r="A58">
-        <v>821</v>
+        <v>811</v>
       </c>
       <c r="B58" t="s">
         <v>90</v>
       </c>
       <c r="C58" s="1">
-        <v>46037</v>
+        <v>46020</v>
       </c>
       <c r="D58" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="E58" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
@@ -5743,22 +5659,22 @@
         <v>28</v>
       </c>
       <c r="I58" s="1">
-        <v>46066</v>
+        <v>46050</v>
       </c>
       <c r="J58" s="1">
-        <v>46097</v>
+        <v>46080</v>
       </c>
       <c r="K58" s="1">
-        <v>46157</v>
+        <v>46140</v>
       </c>
       <c r="L58" s="1">
-        <v>46217</v>
+        <v>46199</v>
       </c>
       <c r="M58" t="s">
         <v>10</v>
       </c>
       <c r="N58" s="1">
-        <v>46157</v>
+        <v>46140</v>
       </c>
       <c r="O58" t="s">
         <v>29</v>
@@ -5767,42 +5683,42 @@
         <v>1</v>
       </c>
       <c r="Q58" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="R58">
-        <v>54862</v>
+        <v>580</v>
       </c>
       <c r="S58">
-        <v>54862</v>
+        <v>3</v>
       </c>
       <c r="T58" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="U58" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="V58">
-        <v>54862</v>
+        <v>580</v>
       </c>
       <c r="W58" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="59" spans="1:23">
       <c r="A59">
-        <v>820</v>
+        <v>810</v>
       </c>
       <c r="B59" t="s">
         <v>91</v>
       </c>
       <c r="C59" s="1">
-        <v>46036</v>
+        <v>46021</v>
       </c>
       <c r="D59" t="s">
-        <v>128</v>
+        <v>24</v>
       </c>
       <c r="E59" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="F59" t="s">
         <v>26</v>
@@ -5814,22 +5730,22 @@
         <v>28</v>
       </c>
       <c r="I59" s="1">
-        <v>46066</v>
+        <v>46051</v>
       </c>
       <c r="J59" s="1">
-        <v>46097</v>
+        <v>46080</v>
       </c>
       <c r="K59" s="1">
-        <v>46156</v>
+        <v>46141</v>
       </c>
       <c r="L59" s="1">
-        <v>46216</v>
+        <v>46202</v>
       </c>
       <c r="M59" t="s">
         <v>10</v>
       </c>
       <c r="N59" s="1">
-        <v>46156</v>
+        <v>46141</v>
       </c>
       <c r="O59" t="s">
         <v>29</v>
@@ -5838,42 +5754,42 @@
         <v>1</v>
       </c>
       <c r="Q59" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="R59">
-        <v>207</v>
+        <v>552</v>
       </c>
       <c r="S59">
-        <v>207</v>
+        <v>3</v>
       </c>
       <c r="T59" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="U59" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="V59">
-        <v>207</v>
+        <v>552</v>
       </c>
       <c r="W59" t="s">
-        <v>376</v>
+        <v>352</v>
       </c>
     </row>
     <row r="60" spans="1:23">
       <c r="A60">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="B60" t="s">
         <v>92</v>
       </c>
       <c r="C60" s="1">
-        <v>46036</v>
+        <v>46020</v>
       </c>
       <c r="D60" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="E60" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
@@ -5885,22 +5801,22 @@
         <v>28</v>
       </c>
       <c r="I60" s="1">
-        <v>46066</v>
+        <v>46050</v>
       </c>
       <c r="J60" s="1">
-        <v>46097</v>
+        <v>46080</v>
       </c>
       <c r="K60" s="1">
-        <v>46156</v>
+        <v>46140</v>
       </c>
       <c r="L60" s="1">
-        <v>46216</v>
+        <v>46199</v>
       </c>
       <c r="M60" t="s">
         <v>10</v>
       </c>
       <c r="N60" s="1">
-        <v>46156</v>
+        <v>46140</v>
       </c>
       <c r="O60" t="s">
         <v>29</v>
@@ -5909,39 +5825,39 @@
         <v>1</v>
       </c>
       <c r="Q60" t="s">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c r="R60">
-        <v>197</v>
+        <v>3505</v>
       </c>
       <c r="S60">
-        <v>197</v>
+        <v>3505</v>
       </c>
       <c r="T60" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="U60" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="V60">
-        <v>197</v>
+        <v>3505</v>
       </c>
       <c r="W60" t="s">
-        <v>376</v>
+        <v>33</v>
       </c>
     </row>
     <row r="61" spans="1:23">
       <c r="A61">
-        <v>818</v>
+        <v>808</v>
       </c>
       <c r="B61" t="s">
         <v>93</v>
       </c>
       <c r="C61" s="1">
-        <v>46035</v>
+        <v>46020</v>
       </c>
       <c r="D61" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="E61" t="s">
         <v>156</v>
@@ -5956,22 +5872,22 @@
         <v>28</v>
       </c>
       <c r="I61" s="1">
-        <v>46065</v>
+        <v>46050</v>
       </c>
       <c r="J61" s="1">
-        <v>46094</v>
+        <v>46080</v>
       </c>
       <c r="K61" s="1">
-        <v>46155</v>
+        <v>46140</v>
       </c>
       <c r="L61" s="1">
-        <v>46216</v>
+        <v>46199</v>
       </c>
       <c r="M61" t="s">
         <v>10</v>
       </c>
       <c r="N61" s="1">
-        <v>46155</v>
+        <v>46140</v>
       </c>
       <c r="O61" t="s">
         <v>29</v>
@@ -5980,42 +5896,42 @@
         <v>1</v>
       </c>
       <c r="Q61" t="s">
-        <v>184</v>
+        <v>30</v>
       </c>
       <c r="R61">
-        <v>15591</v>
+        <v>2777</v>
       </c>
       <c r="S61">
-        <v>15591</v>
+        <v>2777</v>
       </c>
       <c r="T61" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="U61" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="V61">
-        <v>15591</v>
+        <v>2777</v>
       </c>
       <c r="W61" t="s">
-        <v>376</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" spans="1:23">
       <c r="A62">
-        <v>817</v>
+        <v>791</v>
       </c>
       <c r="B62" t="s">
         <v>94</v>
       </c>
       <c r="C62" s="1">
-        <v>46030</v>
+        <v>45996</v>
       </c>
       <c r="D62" t="s">
         <v>24</v>
       </c>
       <c r="E62" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
@@ -6027,22 +5943,22 @@
         <v>28</v>
       </c>
       <c r="I62" s="1">
-        <v>46059</v>
+        <v>46027</v>
       </c>
       <c r="J62" s="1">
-        <v>46090</v>
+        <v>46056</v>
       </c>
       <c r="K62" s="1">
-        <v>46150</v>
+        <v>46115</v>
       </c>
       <c r="L62" s="1">
-        <v>46210</v>
+        <v>46176</v>
       </c>
       <c r="M62" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N62" s="1">
-        <v>46150</v>
+        <v>46176</v>
       </c>
       <c r="O62" t="s">
         <v>29</v>
@@ -6051,42 +5967,42 @@
         <v>1</v>
       </c>
       <c r="Q62" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R62">
-        <v>10238</v>
+        <v>12264</v>
       </c>
       <c r="S62">
-        <v>10238</v>
+        <v>5</v>
       </c>
       <c r="T62" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="U62" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="V62">
-        <v>10238</v>
+        <v>12264</v>
       </c>
       <c r="W62" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="63" spans="1:23">
       <c r="A63">
-        <v>811</v>
+        <v>786</v>
       </c>
       <c r="B63" t="s">
         <v>95</v>
       </c>
       <c r="C63" s="1">
-        <v>46020</v>
+        <v>45995</v>
       </c>
       <c r="D63" t="s">
         <v>24</v>
       </c>
       <c r="E63" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
@@ -6098,22 +6014,22 @@
         <v>28</v>
       </c>
       <c r="I63" s="1">
-        <v>46050</v>
+        <v>46024</v>
       </c>
       <c r="J63" s="1">
-        <v>46080</v>
+        <v>46055</v>
       </c>
       <c r="K63" s="1">
-        <v>46140</v>
+        <v>46115</v>
       </c>
       <c r="L63" s="1">
-        <v>46199</v>
+        <v>46175</v>
       </c>
       <c r="M63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N63" s="1">
-        <v>46140</v>
+        <v>46175</v>
       </c>
       <c r="O63" t="s">
         <v>29</v>
@@ -6122,42 +6038,42 @@
         <v>1</v>
       </c>
       <c r="Q63" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R63">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="S63">
-        <v>3</v>
+        <v>480</v>
       </c>
       <c r="T63" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="U63" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="V63">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="W63" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="64" spans="1:23">
       <c r="A64">
-        <v>810</v>
+        <v>785</v>
       </c>
       <c r="B64" t="s">
         <v>96</v>
       </c>
       <c r="C64" s="1">
-        <v>46021</v>
+        <v>45995</v>
       </c>
       <c r="D64" t="s">
         <v>24</v>
       </c>
       <c r="E64" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
@@ -6169,22 +6085,22 @@
         <v>28</v>
       </c>
       <c r="I64" s="1">
-        <v>46051</v>
+        <v>46024</v>
       </c>
       <c r="J64" s="1">
-        <v>46080</v>
+        <v>46055</v>
       </c>
       <c r="K64" s="1">
-        <v>46141</v>
+        <v>46115</v>
       </c>
       <c r="L64" s="1">
-        <v>46202</v>
+        <v>46175</v>
       </c>
       <c r="M64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N64" s="1">
-        <v>46141</v>
+        <v>46175</v>
       </c>
       <c r="O64" t="s">
         <v>29</v>
@@ -6193,42 +6109,42 @@
         <v>1</v>
       </c>
       <c r="Q64" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R64">
-        <v>552</v>
+        <v>408</v>
       </c>
       <c r="S64">
-        <v>3</v>
+        <v>408</v>
       </c>
       <c r="T64" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="U64" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="V64">
-        <v>552</v>
+        <v>408</v>
       </c>
       <c r="W64" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="65" spans="1:23">
       <c r="A65">
-        <v>809</v>
+        <v>784</v>
       </c>
       <c r="B65" t="s">
         <v>97</v>
       </c>
       <c r="C65" s="1">
-        <v>46020</v>
+        <v>45996</v>
       </c>
       <c r="D65" t="s">
         <v>24</v>
       </c>
       <c r="E65" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
@@ -6240,22 +6156,22 @@
         <v>28</v>
       </c>
       <c r="I65" s="1">
-        <v>46050</v>
+        <v>46027</v>
       </c>
       <c r="J65" s="1">
-        <v>46080</v>
+        <v>46056</v>
       </c>
       <c r="K65" s="1">
-        <v>46140</v>
+        <v>46115</v>
       </c>
       <c r="L65" s="1">
-        <v>46199</v>
+        <v>46176</v>
       </c>
       <c r="M65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N65" s="1">
-        <v>46140</v>
+        <v>46176</v>
       </c>
       <c r="O65" t="s">
         <v>29</v>
@@ -6264,42 +6180,42 @@
         <v>1</v>
       </c>
       <c r="Q65" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="R65">
-        <v>3505</v>
+        <v>355</v>
       </c>
       <c r="S65">
-        <v>3505</v>
+        <v>355</v>
       </c>
       <c r="T65" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="U65" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="V65">
-        <v>3505</v>
+        <v>355</v>
       </c>
       <c r="W65" t="s">
-        <v>381</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:23">
       <c r="A66">
-        <v>808</v>
+        <v>783</v>
       </c>
       <c r="B66" t="s">
         <v>98</v>
       </c>
       <c r="C66" s="1">
-        <v>46020</v>
+        <v>45995</v>
       </c>
       <c r="D66" t="s">
         <v>24</v>
       </c>
       <c r="E66" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
@@ -6311,22 +6227,22 @@
         <v>28</v>
       </c>
       <c r="I66" s="1">
-        <v>46050</v>
+        <v>46024</v>
       </c>
       <c r="J66" s="1">
-        <v>46080</v>
+        <v>46055</v>
       </c>
       <c r="K66" s="1">
-        <v>46140</v>
+        <v>46115</v>
       </c>
       <c r="L66" s="1">
-        <v>46199</v>
+        <v>46175</v>
       </c>
       <c r="M66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N66" s="1">
-        <v>46140</v>
+        <v>46175</v>
       </c>
       <c r="O66" t="s">
         <v>29</v>
@@ -6335,42 +6251,42 @@
         <v>1</v>
       </c>
       <c r="Q66" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="R66">
-        <v>2777</v>
+        <v>1392</v>
       </c>
       <c r="S66">
-        <v>2777</v>
+        <v>1392</v>
       </c>
       <c r="T66" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="U66" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="V66">
-        <v>2777</v>
+        <v>1392</v>
       </c>
       <c r="W66" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
     <row r="67" spans="1:23">
       <c r="A67">
-        <v>807</v>
+        <v>782</v>
       </c>
       <c r="B67" t="s">
         <v>99</v>
       </c>
       <c r="C67" s="1">
-        <v>46018</v>
+        <v>45995</v>
       </c>
       <c r="D67" t="s">
         <v>24</v>
       </c>
       <c r="E67" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F67" t="s">
         <v>26</v>
@@ -6382,22 +6298,22 @@
         <v>28</v>
       </c>
       <c r="I67" s="1">
-        <v>46048</v>
+        <v>46024</v>
       </c>
       <c r="J67" s="1">
-        <v>46078</v>
+        <v>46055</v>
       </c>
       <c r="K67" s="1">
-        <v>46139</v>
+        <v>46115</v>
       </c>
       <c r="L67" s="1">
-        <v>46198</v>
+        <v>46175</v>
       </c>
       <c r="M67" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N67" s="1">
-        <v>46139</v>
+        <v>46175</v>
       </c>
       <c r="O67" t="s">
         <v>29</v>
@@ -6406,42 +6322,42 @@
         <v>1</v>
       </c>
       <c r="Q67" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R67">
-        <v>12408</v>
+        <v>4256</v>
       </c>
       <c r="S67">
-        <v>5</v>
+        <v>4256</v>
       </c>
       <c r="T67" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="U67" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="V67">
-        <v>12408</v>
+        <v>4256</v>
       </c>
       <c r="W67" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="68" spans="1:23">
       <c r="A68">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="B68" t="s">
         <v>100</v>
       </c>
       <c r="C68" s="1">
-        <v>45996</v>
+        <v>45985</v>
       </c>
       <c r="D68" t="s">
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="F68" t="s">
         <v>26</v>
@@ -6453,22 +6369,22 @@
         <v>28</v>
       </c>
       <c r="I68" s="1">
-        <v>46027</v>
+        <v>46015</v>
       </c>
       <c r="J68" s="1">
-        <v>46056</v>
+        <v>46045</v>
       </c>
       <c r="K68" s="1">
-        <v>46115</v>
+        <v>46105</v>
       </c>
       <c r="L68" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="M68" t="s">
         <v>11</v>
       </c>
       <c r="N68" s="1">
-        <v>46176</v>
+        <v>46164</v>
       </c>
       <c r="O68" t="s">
         <v>29</v>
@@ -6477,42 +6393,42 @@
         <v>1</v>
       </c>
       <c r="Q68" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R68">
-        <v>12264</v>
+        <v>81568</v>
       </c>
       <c r="S68">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T68" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="U68" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="V68">
-        <v>12264</v>
+        <v>81568</v>
       </c>
       <c r="W68" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="69" spans="1:23">
       <c r="A69">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="B69" t="s">
         <v>101</v>
       </c>
       <c r="C69" s="1">
-        <v>45995</v>
+        <v>45979</v>
       </c>
       <c r="D69" t="s">
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="F69" t="s">
         <v>26</v>
@@ -6524,22 +6440,22 @@
         <v>28</v>
       </c>
       <c r="I69" s="1">
-        <v>46024</v>
+        <v>46009</v>
       </c>
       <c r="J69" s="1">
-        <v>46055</v>
+        <v>46038</v>
       </c>
       <c r="K69" s="1">
-        <v>46115</v>
+        <v>46099</v>
       </c>
       <c r="L69" s="1">
-        <v>46175</v>
+        <v>46160</v>
       </c>
       <c r="M69" t="s">
         <v>11</v>
       </c>
       <c r="N69" s="1">
-        <v>46175</v>
+        <v>46160</v>
       </c>
       <c r="O69" t="s">
         <v>29</v>
@@ -6548,42 +6464,42 @@
         <v>1</v>
       </c>
       <c r="Q69" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R69">
-        <v>480</v>
+        <v>1032</v>
       </c>
       <c r="S69">
-        <v>480</v>
+        <v>15</v>
       </c>
       <c r="T69" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="U69" t="s">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="V69">
-        <v>480</v>
+        <v>1032</v>
       </c>
       <c r="W69" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="70" spans="1:23">
       <c r="A70">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="B70" t="s">
         <v>102</v>
       </c>
       <c r="C70" s="1">
-        <v>45995</v>
+        <v>45979</v>
       </c>
       <c r="D70" t="s">
         <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F70" t="s">
         <v>26</v>
@@ -6595,22 +6511,22 @@
         <v>28</v>
       </c>
       <c r="I70" s="1">
-        <v>46024</v>
+        <v>46009</v>
       </c>
       <c r="J70" s="1">
-        <v>46055</v>
+        <v>46038</v>
       </c>
       <c r="K70" s="1">
-        <v>46115</v>
+        <v>46099</v>
       </c>
       <c r="L70" s="1">
-        <v>46175</v>
+        <v>46160</v>
       </c>
       <c r="M70" t="s">
         <v>11</v>
       </c>
       <c r="N70" s="1">
-        <v>46175</v>
+        <v>46160</v>
       </c>
       <c r="O70" t="s">
         <v>29</v>
@@ -6619,42 +6535,42 @@
         <v>1</v>
       </c>
       <c r="Q70" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R70">
-        <v>408</v>
+        <v>32016</v>
       </c>
       <c r="S70">
-        <v>408</v>
+        <v>24</v>
       </c>
       <c r="T70" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="U70" t="s">
-        <v>351</v>
+        <v>331</v>
       </c>
       <c r="V70">
-        <v>408</v>
+        <v>32016</v>
       </c>
       <c r="W70" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="71" spans="1:23">
       <c r="A71">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="B71" t="s">
         <v>103</v>
       </c>
       <c r="C71" s="1">
-        <v>45996</v>
+        <v>45978</v>
       </c>
       <c r="D71" t="s">
         <v>24</v>
       </c>
       <c r="E71" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="F71" t="s">
         <v>26</v>
@@ -6666,22 +6582,22 @@
         <v>28</v>
       </c>
       <c r="I71" s="1">
-        <v>46027</v>
+        <v>46008</v>
       </c>
       <c r="J71" s="1">
-        <v>46056</v>
+        <v>46038</v>
       </c>
       <c r="K71" s="1">
-        <v>46115</v>
+        <v>46098</v>
       </c>
       <c r="L71" s="1">
-        <v>46176</v>
+        <v>46157</v>
       </c>
       <c r="M71" t="s">
         <v>11</v>
       </c>
       <c r="N71" s="1">
-        <v>46176</v>
+        <v>46157</v>
       </c>
       <c r="O71" t="s">
         <v>29</v>
@@ -6690,42 +6606,42 @@
         <v>1</v>
       </c>
       <c r="Q71" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="R71">
-        <v>1741</v>
+        <v>1592</v>
       </c>
       <c r="S71">
-        <v>1741</v>
+        <v>8</v>
       </c>
       <c r="T71" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="U71" t="s">
+        <v>332</v>
+      </c>
+      <c r="V71">
+        <v>1592</v>
+      </c>
+      <c r="W71" t="s">
         <v>352</v>
-      </c>
-      <c r="V71">
-        <v>1741</v>
-      </c>
-      <c r="W71" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="72" spans="1:23">
       <c r="A72">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="B72" t="s">
         <v>104</v>
       </c>
       <c r="C72" s="1">
-        <v>45995</v>
+        <v>45974</v>
       </c>
       <c r="D72" t="s">
         <v>24</v>
       </c>
       <c r="E72" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F72" t="s">
         <v>26</v>
@@ -6737,22 +6653,22 @@
         <v>28</v>
       </c>
       <c r="I72" s="1">
-        <v>46024</v>
+        <v>46003</v>
       </c>
       <c r="J72" s="1">
-        <v>46055</v>
+        <v>46034</v>
       </c>
       <c r="K72" s="1">
-        <v>46115</v>
+        <v>46094</v>
       </c>
       <c r="L72" s="1">
-        <v>46175</v>
+        <v>46154</v>
       </c>
       <c r="M72" t="s">
         <v>11</v>
       </c>
       <c r="N72" s="1">
-        <v>46175</v>
+        <v>46154</v>
       </c>
       <c r="O72" t="s">
         <v>29</v>
@@ -6761,42 +6677,42 @@
         <v>1</v>
       </c>
       <c r="Q72" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R72">
-        <v>1392</v>
+        <v>1407</v>
       </c>
       <c r="S72">
-        <v>1392</v>
+        <v>1407</v>
       </c>
       <c r="T72" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="U72" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
       <c r="V72">
-        <v>1392</v>
+        <v>1407</v>
       </c>
       <c r="W72" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="73" spans="1:23">
       <c r="A73">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="B73" t="s">
         <v>105</v>
       </c>
       <c r="C73" s="1">
-        <v>45995</v>
+        <v>45974</v>
       </c>
       <c r="D73" t="s">
         <v>24</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F73" t="s">
         <v>26</v>
@@ -6808,22 +6724,22 @@
         <v>28</v>
       </c>
       <c r="I73" s="1">
-        <v>46024</v>
+        <v>46003</v>
       </c>
       <c r="J73" s="1">
-        <v>46055</v>
+        <v>46034</v>
       </c>
       <c r="K73" s="1">
-        <v>46115</v>
+        <v>46094</v>
       </c>
       <c r="L73" s="1">
-        <v>46175</v>
+        <v>46154</v>
       </c>
       <c r="M73" t="s">
         <v>11</v>
       </c>
       <c r="N73" s="1">
-        <v>46175</v>
+        <v>46154</v>
       </c>
       <c r="O73" t="s">
         <v>29</v>
@@ -6835,19 +6751,19 @@
         <v>30</v>
       </c>
       <c r="R73">
-        <v>4256</v>
+        <v>1224</v>
       </c>
       <c r="S73">
-        <v>4256</v>
+        <v>1224</v>
       </c>
       <c r="T73" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="U73" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="V73">
-        <v>4256</v>
+        <v>1224</v>
       </c>
       <c r="W73" t="s">
         <v>33</v>
@@ -6855,19 +6771,19 @@
     </row>
     <row r="74" spans="1:23">
       <c r="A74">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="B74" t="s">
         <v>106</v>
       </c>
       <c r="C74" s="1">
-        <v>45985</v>
+        <v>45974</v>
       </c>
       <c r="D74" t="s">
         <v>24</v>
       </c>
       <c r="E74" t="s">
-        <v>143</v>
+        <v>166</v>
       </c>
       <c r="F74" t="s">
         <v>26</v>
@@ -6879,22 +6795,22 @@
         <v>28</v>
       </c>
       <c r="I74" s="1">
-        <v>46015</v>
+        <v>46003</v>
       </c>
       <c r="J74" s="1">
-        <v>46045</v>
+        <v>46034</v>
       </c>
       <c r="K74" s="1">
-        <v>46105</v>
+        <v>46094</v>
       </c>
       <c r="L74" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="M74" t="s">
         <v>11</v>
       </c>
       <c r="N74" s="1">
-        <v>46164</v>
+        <v>46154</v>
       </c>
       <c r="O74" t="s">
         <v>29</v>
@@ -6906,19 +6822,19 @@
         <v>30</v>
       </c>
       <c r="R74">
-        <v>81568</v>
+        <v>1194</v>
       </c>
       <c r="S74">
-        <v>40</v>
+        <v>1194</v>
       </c>
       <c r="T74" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="U74" t="s">
-        <v>355</v>
+        <v>335</v>
       </c>
       <c r="V74">
-        <v>81568</v>
+        <v>1194</v>
       </c>
       <c r="W74" t="s">
         <v>33</v>
@@ -6926,19 +6842,19 @@
     </row>
     <row r="75" spans="1:23">
       <c r="A75">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="B75" t="s">
         <v>107</v>
       </c>
       <c r="C75" s="1">
-        <v>45979</v>
+        <v>45973</v>
       </c>
       <c r="D75" t="s">
         <v>24</v>
       </c>
       <c r="E75" t="s">
-        <v>144</v>
+        <v>167</v>
       </c>
       <c r="F75" t="s">
         <v>26</v>
@@ -6950,22 +6866,22 @@
         <v>28</v>
       </c>
       <c r="I75" s="1">
-        <v>46009</v>
+        <v>46003</v>
       </c>
       <c r="J75" s="1">
-        <v>46038</v>
+        <v>46034</v>
       </c>
       <c r="K75" s="1">
-        <v>46099</v>
+        <v>46093</v>
       </c>
       <c r="L75" s="1">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="M75" t="s">
         <v>11</v>
       </c>
       <c r="N75" s="1">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="O75" t="s">
         <v>29</v>
@@ -6977,19 +6893,19 @@
         <v>30</v>
       </c>
       <c r="R75">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="S75">
-        <v>15</v>
+        <v>1059</v>
       </c>
       <c r="T75" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="U75" t="s">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="V75">
-        <v>1032</v>
+        <v>1059</v>
       </c>
       <c r="W75" t="s">
         <v>33</v>
@@ -6997,19 +6913,19 @@
     </row>
     <row r="76" spans="1:23">
       <c r="A76">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="B76" t="s">
         <v>108</v>
       </c>
       <c r="C76" s="1">
-        <v>45979</v>
+        <v>45973</v>
       </c>
       <c r="D76" t="s">
         <v>24</v>
       </c>
       <c r="E76" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F76" t="s">
         <v>26</v>
@@ -7021,22 +6937,22 @@
         <v>28</v>
       </c>
       <c r="I76" s="1">
-        <v>46009</v>
+        <v>46003</v>
       </c>
       <c r="J76" s="1">
-        <v>46038</v>
+        <v>46034</v>
       </c>
       <c r="K76" s="1">
-        <v>46099</v>
+        <v>46093</v>
       </c>
       <c r="L76" s="1">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="M76" t="s">
         <v>11</v>
       </c>
       <c r="N76" s="1">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="O76" t="s">
         <v>29</v>
@@ -7048,19 +6964,19 @@
         <v>30</v>
       </c>
       <c r="R76">
-        <v>32016</v>
+        <v>1387</v>
       </c>
       <c r="S76">
-        <v>24</v>
+        <v>1387</v>
       </c>
       <c r="T76" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="U76" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
       <c r="V76">
-        <v>32016</v>
+        <v>1387</v>
       </c>
       <c r="W76" t="s">
         <v>33</v>
@@ -7068,19 +6984,19 @@
     </row>
     <row r="77" spans="1:23">
       <c r="A77">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="B77" t="s">
         <v>109</v>
       </c>
       <c r="C77" s="1">
-        <v>45978</v>
+        <v>45973</v>
       </c>
       <c r="D77" t="s">
         <v>24</v>
       </c>
       <c r="E77" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="F77" t="s">
         <v>26</v>
@@ -7092,22 +7008,22 @@
         <v>28</v>
       </c>
       <c r="I77" s="1">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="J77" s="1">
-        <v>46038</v>
+        <v>46034</v>
       </c>
       <c r="K77" s="1">
-        <v>46098</v>
+        <v>46093</v>
       </c>
       <c r="L77" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="M77" t="s">
         <v>11</v>
       </c>
       <c r="N77" s="1">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="O77" t="s">
         <v>29</v>
@@ -7119,19 +7035,19 @@
         <v>30</v>
       </c>
       <c r="R77">
-        <v>1592</v>
+        <v>1495</v>
       </c>
       <c r="S77">
-        <v>8</v>
+        <v>1495</v>
       </c>
       <c r="T77" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="U77" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="V77">
-        <v>1592</v>
+        <v>1495</v>
       </c>
       <c r="W77" t="s">
         <v>33</v>
@@ -7139,19 +7055,19 @@
     </row>
     <row r="78" spans="1:23">
       <c r="A78">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="B78" t="s">
         <v>110</v>
       </c>
       <c r="C78" s="1">
-        <v>45974</v>
+        <v>45972</v>
       </c>
       <c r="D78" t="s">
         <v>24</v>
       </c>
       <c r="E78" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="F78" t="s">
         <v>26</v>
@@ -7163,22 +7079,22 @@
         <v>28</v>
       </c>
       <c r="I78" s="1">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="J78" s="1">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="K78" s="1">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="L78" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="M78" t="s">
         <v>11</v>
       </c>
       <c r="N78" s="1">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="O78" t="s">
         <v>29</v>
@@ -7187,42 +7103,42 @@
         <v>1</v>
       </c>
       <c r="Q78" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R78">
-        <v>1407</v>
+        <v>4234</v>
       </c>
       <c r="S78">
-        <v>1407</v>
+        <v>8</v>
       </c>
       <c r="T78" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="U78" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="V78">
-        <v>1407</v>
+        <v>4234</v>
       </c>
       <c r="W78" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="79" spans="1:23">
       <c r="A79">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="B79" t="s">
         <v>111</v>
       </c>
       <c r="C79" s="1">
-        <v>45974</v>
+        <v>45971</v>
       </c>
       <c r="D79" t="s">
         <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F79" t="s">
         <v>26</v>
@@ -7234,22 +7150,22 @@
         <v>28</v>
       </c>
       <c r="I79" s="1">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="J79" s="1">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="K79" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
       <c r="L79" s="1">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="M79" t="s">
         <v>11</v>
       </c>
       <c r="N79" s="1">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="O79" t="s">
         <v>29</v>
@@ -7258,42 +7174,42 @@
         <v>1</v>
       </c>
       <c r="Q79" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="R79">
-        <v>1224</v>
+        <v>2726</v>
       </c>
       <c r="S79">
-        <v>1224</v>
+        <v>3</v>
       </c>
       <c r="T79" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="U79" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="V79">
-        <v>1224</v>
+        <v>2726</v>
       </c>
       <c r="W79" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
     <row r="80" spans="1:23">
       <c r="A80">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="B80" t="s">
         <v>112</v>
       </c>
       <c r="C80" s="1">
-        <v>45974</v>
+        <v>45971</v>
       </c>
       <c r="D80" t="s">
         <v>24</v>
       </c>
       <c r="E80" t="s">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="F80" t="s">
         <v>26</v>
@@ -7305,22 +7221,22 @@
         <v>28</v>
       </c>
       <c r="I80" s="1">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="J80" s="1">
-        <v>46034</v>
+        <v>46031</v>
       </c>
       <c r="K80" s="1">
-        <v>46094</v>
+        <v>46091</v>
       </c>
       <c r="L80" s="1">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="M80" t="s">
         <v>11</v>
       </c>
       <c r="N80" s="1">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="O80" t="s">
         <v>29</v>
@@ -7329,42 +7245,42 @@
         <v>1</v>
       </c>
       <c r="Q80" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="R80">
-        <v>1194</v>
+        <v>7746</v>
       </c>
       <c r="S80">
-        <v>1194</v>
+        <v>6</v>
       </c>
       <c r="T80" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="U80" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="V80">
-        <v>1194</v>
+        <v>7746</v>
       </c>
       <c r="W80" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
     <row r="81" spans="1:23">
       <c r="A81">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="B81" t="s">
         <v>113</v>
       </c>
       <c r="C81" s="1">
-        <v>45973</v>
+        <v>45966</v>
       </c>
       <c r="D81" t="s">
         <v>24</v>
       </c>
       <c r="E81" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F81" t="s">
         <v>26</v>
@@ -7376,22 +7292,22 @@
         <v>28</v>
       </c>
       <c r="I81" s="1">
-        <v>46003</v>
+        <v>45996</v>
       </c>
       <c r="J81" s="1">
-        <v>46034</v>
+        <v>46027</v>
       </c>
       <c r="K81" s="1">
-        <v>46093</v>
+        <v>46086</v>
       </c>
       <c r="L81" s="1">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="M81" t="s">
         <v>11</v>
       </c>
       <c r="N81" s="1">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="O81" t="s">
         <v>29</v>
@@ -7400,42 +7316,42 @@
         <v>1</v>
       </c>
       <c r="Q81" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="R81">
-        <v>1059</v>
+        <v>151</v>
       </c>
       <c r="S81">
-        <v>1059</v>
+        <v>151</v>
       </c>
       <c r="T81" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="U81" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="V81">
-        <v>1059</v>
+        <v>151</v>
       </c>
       <c r="W81" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
     <row r="82" spans="1:23">
       <c r="A82">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="B82" t="s">
         <v>114</v>
       </c>
       <c r="C82" s="1">
-        <v>45973</v>
+        <v>45964</v>
       </c>
       <c r="D82" t="s">
         <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="F82" t="s">
         <v>26</v>
@@ -7447,22 +7363,22 @@
         <v>28</v>
       </c>
       <c r="I82" s="1">
-        <v>46003</v>
+        <v>45994</v>
       </c>
       <c r="J82" s="1">
-        <v>46034</v>
+        <v>46024</v>
       </c>
       <c r="K82" s="1">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="L82" s="1">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="M82" t="s">
         <v>11</v>
       </c>
       <c r="N82" s="1">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="O82" t="s">
         <v>29</v>
@@ -7471,42 +7387,42 @@
         <v>1</v>
       </c>
       <c r="Q82" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="R82">
-        <v>1387</v>
+        <v>1403</v>
       </c>
       <c r="S82">
-        <v>1387</v>
+        <v>6</v>
       </c>
       <c r="T82" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="U82" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
       <c r="V82">
-        <v>1387</v>
+        <v>1403</v>
       </c>
       <c r="W82" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:23">
       <c r="A83">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="B83" t="s">
         <v>115</v>
       </c>
       <c r="C83" s="1">
-        <v>45973</v>
+        <v>45964</v>
       </c>
       <c r="D83" t="s">
         <v>24</v>
       </c>
       <c r="E83" t="s">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="F83" t="s">
         <v>26</v>
@@ -7518,22 +7434,22 @@
         <v>28</v>
       </c>
       <c r="I83" s="1">
-        <v>46003</v>
+        <v>45994</v>
       </c>
       <c r="J83" s="1">
-        <v>46034</v>
+        <v>46024</v>
       </c>
       <c r="K83" s="1">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="L83" s="1">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="M83" t="s">
         <v>11</v>
       </c>
       <c r="N83" s="1">
-        <v>46153</v>
+        <v>46143</v>
       </c>
       <c r="O83" t="s">
         <v>29</v>
@@ -7542,42 +7458,42 @@
         <v>1</v>
       </c>
       <c r="Q83" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="R83">
-        <v>1495</v>
+        <v>5049</v>
       </c>
       <c r="S83">
-        <v>1495</v>
+        <v>664</v>
       </c>
       <c r="T83" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="U83" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="V83">
-        <v>1495</v>
+        <v>5049</v>
       </c>
       <c r="W83" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
     </row>
     <row r="84" spans="1:23">
       <c r="A84">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="B84" t="s">
         <v>116</v>
       </c>
       <c r="C84" s="1">
-        <v>45972</v>
+        <v>45961</v>
       </c>
       <c r="D84" t="s">
         <v>24</v>
       </c>
       <c r="E84" t="s">
-        <v>171</v>
+        <v>125</v>
       </c>
       <c r="F84" t="s">
         <v>26</v>
@@ -7589,22 +7505,22 @@
         <v>28</v>
       </c>
       <c r="I84" s="1">
-        <v>46002</v>
+        <v>45992</v>
       </c>
       <c r="J84" s="1">
-        <v>46031</v>
+        <v>46021</v>
       </c>
       <c r="K84" s="1">
-        <v>46092</v>
+        <v>46080</v>
       </c>
       <c r="L84" s="1">
-        <v>46153</v>
+        <v>46141</v>
       </c>
       <c r="M84" t="s">
         <v>11</v>
       </c>
       <c r="N84" s="1">
-        <v>46153</v>
+        <v>46141</v>
       </c>
       <c r="O84" t="s">
         <v>29</v>
@@ -7613,42 +7529,42 @@
         <v>1</v>
       </c>
       <c r="Q84" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R84">
-        <v>4234</v>
+        <v>772</v>
       </c>
       <c r="S84">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T84" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="U84" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="V84">
-        <v>4234</v>
+        <v>772</v>
       </c>
       <c r="W84" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="85" spans="1:23">
       <c r="A85">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="B85" t="s">
         <v>117</v>
       </c>
       <c r="C85" s="1">
-        <v>45971</v>
+        <v>45961</v>
       </c>
       <c r="D85" t="s">
         <v>24</v>
       </c>
       <c r="E85" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="F85" t="s">
         <v>26</v>
@@ -7660,22 +7576,22 @@
         <v>28</v>
       </c>
       <c r="I85" s="1">
-        <v>46001</v>
+        <v>45992</v>
       </c>
       <c r="J85" s="1">
-        <v>46031</v>
+        <v>46021</v>
       </c>
       <c r="K85" s="1">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="L85" s="1">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="M85" t="s">
         <v>11</v>
       </c>
       <c r="N85" s="1">
-        <v>46150</v>
+        <v>46141</v>
       </c>
       <c r="O85" t="s">
         <v>29</v>
@@ -7684,42 +7600,42 @@
         <v>1</v>
       </c>
       <c r="Q85" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R85">
-        <v>2726</v>
+        <v>11688</v>
       </c>
       <c r="S85">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T85" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="U85" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="V85">
-        <v>2726</v>
+        <v>11688</v>
       </c>
       <c r="W85" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:23">
       <c r="A86">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="B86" t="s">
         <v>118</v>
       </c>
       <c r="C86" s="1">
-        <v>45971</v>
+        <v>45960</v>
       </c>
       <c r="D86" t="s">
         <v>24</v>
       </c>
       <c r="E86" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="F86" t="s">
         <v>26</v>
@@ -7731,22 +7647,22 @@
         <v>28</v>
       </c>
       <c r="I86" s="1">
-        <v>46001</v>
+        <v>45989</v>
       </c>
       <c r="J86" s="1">
-        <v>46031</v>
+        <v>46020</v>
       </c>
       <c r="K86" s="1">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="L86" s="1">
-        <v>46150</v>
+        <v>46140</v>
       </c>
       <c r="M86" t="s">
         <v>11</v>
       </c>
       <c r="N86" s="1">
-        <v>46150</v>
+        <v>46140</v>
       </c>
       <c r="O86" t="s">
         <v>29</v>
@@ -7755,593 +7671,25 @@
         <v>1</v>
       </c>
       <c r="Q86" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="R86">
-        <v>7746</v>
+        <v>8130</v>
       </c>
       <c r="S86">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T86" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="U86" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="V86">
-        <v>7746</v>
+        <v>8130</v>
       </c>
       <c r="W86" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23">
-      <c r="A87">
-        <v>767</v>
-      </c>
-      <c r="B87" t="s">
-        <v>119</v>
-      </c>
-      <c r="C87" s="1">
-        <v>45967</v>
-      </c>
-      <c r="D87" t="s">
-        <v>24</v>
-      </c>
-      <c r="E87" t="s">
-        <v>183</v>
-      </c>
-      <c r="F87" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" t="s">
-        <v>27</v>
-      </c>
-      <c r="H87" t="s">
-        <v>28</v>
-      </c>
-      <c r="I87" s="1">
-        <v>45996</v>
-      </c>
-      <c r="J87" s="1">
-        <v>46027</v>
-      </c>
-      <c r="K87" s="1">
-        <v>46087</v>
-      </c>
-      <c r="L87" s="1">
-        <v>46147</v>
-      </c>
-      <c r="M87" t="s">
-        <v>11</v>
-      </c>
-      <c r="N87" s="1">
-        <v>46147</v>
-      </c>
-      <c r="O87" t="s">
-        <v>29</v>
-      </c>
-      <c r="P87">
-        <v>1</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>189</v>
-      </c>
-      <c r="R87">
-        <v>3864</v>
-      </c>
-      <c r="S87">
-        <v>3864</v>
-      </c>
-      <c r="T87" t="s">
-        <v>275</v>
-      </c>
-      <c r="U87" t="s">
-        <v>368</v>
-      </c>
-      <c r="V87">
-        <v>3864</v>
-      </c>
-      <c r="W87" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="88" spans="1:23">
-      <c r="A88">
-        <v>763</v>
-      </c>
-      <c r="B88" t="s">
-        <v>120</v>
-      </c>
-      <c r="C88" s="1">
-        <v>45964</v>
-      </c>
-      <c r="D88" t="s">
-        <v>24</v>
-      </c>
-      <c r="E88" t="s">
-        <v>143</v>
-      </c>
-      <c r="F88" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" t="s">
-        <v>27</v>
-      </c>
-      <c r="H88" t="s">
-        <v>28</v>
-      </c>
-      <c r="I88" s="1">
-        <v>45994</v>
-      </c>
-      <c r="J88" s="1">
-        <v>46024</v>
-      </c>
-      <c r="K88" s="1">
-        <v>46084</v>
-      </c>
-      <c r="L88" s="1">
-        <v>46143</v>
-      </c>
-      <c r="M88" t="s">
-        <v>11</v>
-      </c>
-      <c r="N88" s="1">
-        <v>46143</v>
-      </c>
-      <c r="O88" t="s">
-        <v>29</v>
-      </c>
-      <c r="P88">
-        <v>1</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>30</v>
-      </c>
-      <c r="R88">
-        <v>1403</v>
-      </c>
-      <c r="S88">
-        <v>6</v>
-      </c>
-      <c r="T88" t="s">
-        <v>276</v>
-      </c>
-      <c r="U88" t="s">
-        <v>369</v>
-      </c>
-      <c r="V88">
-        <v>1403</v>
-      </c>
-      <c r="W88" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="89" spans="1:23">
-      <c r="A89">
-        <v>760</v>
-      </c>
-      <c r="B89" t="s">
-        <v>121</v>
-      </c>
-      <c r="C89" s="1">
-        <v>45964</v>
-      </c>
-      <c r="D89" t="s">
-        <v>24</v>
-      </c>
-      <c r="E89" t="s">
-        <v>142</v>
-      </c>
-      <c r="F89" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" t="s">
-        <v>27</v>
-      </c>
-      <c r="H89" t="s">
-        <v>28</v>
-      </c>
-      <c r="I89" s="1">
-        <v>45994</v>
-      </c>
-      <c r="J89" s="1">
-        <v>46024</v>
-      </c>
-      <c r="K89" s="1">
-        <v>46084</v>
-      </c>
-      <c r="L89" s="1">
-        <v>46143</v>
-      </c>
-      <c r="M89" t="s">
-        <v>11</v>
-      </c>
-      <c r="N89" s="1">
-        <v>46143</v>
-      </c>
-      <c r="O89" t="s">
-        <v>29</v>
-      </c>
-      <c r="P89">
-        <v>1</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>30</v>
-      </c>
-      <c r="R89">
-        <v>5049</v>
-      </c>
-      <c r="S89">
-        <v>664</v>
-      </c>
-      <c r="T89" t="s">
-        <v>277</v>
-      </c>
-      <c r="U89" t="s">
-        <v>370</v>
-      </c>
-      <c r="V89">
-        <v>5049</v>
-      </c>
-      <c r="W89" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="90" spans="1:23">
-      <c r="A90">
-        <v>758</v>
-      </c>
-      <c r="B90" t="s">
-        <v>122</v>
-      </c>
-      <c r="C90" s="1">
-        <v>45961</v>
-      </c>
-      <c r="D90" t="s">
-        <v>24</v>
-      </c>
-      <c r="E90" t="s">
-        <v>133</v>
-      </c>
-      <c r="F90" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" t="s">
-        <v>27</v>
-      </c>
-      <c r="H90" t="s">
-        <v>28</v>
-      </c>
-      <c r="I90" s="1">
-        <v>45992</v>
-      </c>
-      <c r="J90" s="1">
-        <v>46021</v>
-      </c>
-      <c r="K90" s="1">
-        <v>46080</v>
-      </c>
-      <c r="L90" s="1">
-        <v>46141</v>
-      </c>
-      <c r="M90" t="s">
-        <v>11</v>
-      </c>
-      <c r="N90" s="1">
-        <v>46141</v>
-      </c>
-      <c r="O90" t="s">
-        <v>29</v>
-      </c>
-      <c r="P90">
-        <v>1</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>30</v>
-      </c>
-      <c r="R90">
-        <v>772</v>
-      </c>
-      <c r="S90">
-        <v>1</v>
-      </c>
-      <c r="T90" t="s">
-        <v>278</v>
-      </c>
-      <c r="U90" t="s">
-        <v>371</v>
-      </c>
-      <c r="V90">
-        <v>772</v>
-      </c>
-      <c r="W90" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="91" spans="1:23">
-      <c r="A91">
-        <v>757</v>
-      </c>
-      <c r="B91" t="s">
-        <v>123</v>
-      </c>
-      <c r="C91" s="1">
-        <v>45961</v>
-      </c>
-      <c r="D91" t="s">
-        <v>24</v>
-      </c>
-      <c r="E91" t="s">
-        <v>176</v>
-      </c>
-      <c r="F91" t="s">
-        <v>26</v>
-      </c>
-      <c r="G91" t="s">
-        <v>27</v>
-      </c>
-      <c r="H91" t="s">
-        <v>28</v>
-      </c>
-      <c r="I91" s="1">
-        <v>45992</v>
-      </c>
-      <c r="J91" s="1">
-        <v>46021</v>
-      </c>
-      <c r="K91" s="1">
-        <v>46080</v>
-      </c>
-      <c r="L91" s="1">
-        <v>46141</v>
-      </c>
-      <c r="M91" t="s">
-        <v>11</v>
-      </c>
-      <c r="N91" s="1">
-        <v>46141</v>
-      </c>
-      <c r="O91" t="s">
-        <v>29</v>
-      </c>
-      <c r="P91">
-        <v>1</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>30</v>
-      </c>
-      <c r="R91">
-        <v>11688</v>
-      </c>
-      <c r="S91">
-        <v>10</v>
-      </c>
-      <c r="T91" t="s">
-        <v>279</v>
-      </c>
-      <c r="U91" t="s">
-        <v>372</v>
-      </c>
-      <c r="V91">
-        <v>11688</v>
-      </c>
-      <c r="W91" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23">
-      <c r="A92">
-        <v>756</v>
-      </c>
-      <c r="B92" t="s">
-        <v>124</v>
-      </c>
-      <c r="C92" s="1">
-        <v>45960</v>
-      </c>
-      <c r="D92" t="s">
-        <v>24</v>
-      </c>
-      <c r="E92" t="s">
-        <v>168</v>
-      </c>
-      <c r="F92" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" t="s">
-        <v>27</v>
-      </c>
-      <c r="H92" t="s">
-        <v>28</v>
-      </c>
-      <c r="I92" s="1">
-        <v>45989</v>
-      </c>
-      <c r="J92" s="1">
-        <v>46020</v>
-      </c>
-      <c r="K92" s="1">
-        <v>46080</v>
-      </c>
-      <c r="L92" s="1">
-        <v>46140</v>
-      </c>
-      <c r="M92" t="s">
-        <v>11</v>
-      </c>
-      <c r="N92" s="1">
-        <v>46140</v>
-      </c>
-      <c r="O92" t="s">
-        <v>29</v>
-      </c>
-      <c r="P92">
-        <v>1</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>30</v>
-      </c>
-      <c r="R92">
-        <v>8130</v>
-      </c>
-      <c r="S92">
-        <v>7</v>
-      </c>
-      <c r="T92" t="s">
-        <v>280</v>
-      </c>
-      <c r="U92" t="s">
-        <v>373</v>
-      </c>
-      <c r="V92">
-        <v>8130</v>
-      </c>
-      <c r="W92" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23">
-      <c r="A93">
-        <v>753</v>
-      </c>
-      <c r="B93" t="s">
-        <v>125</v>
-      </c>
-      <c r="C93" s="1">
-        <v>45959</v>
-      </c>
-      <c r="D93" t="s">
-        <v>24</v>
-      </c>
-      <c r="E93" t="s">
-        <v>175</v>
-      </c>
-      <c r="F93" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" t="s">
-        <v>27</v>
-      </c>
-      <c r="H93" t="s">
-        <v>28</v>
-      </c>
-      <c r="I93" s="1">
-        <v>45989</v>
-      </c>
-      <c r="J93" s="1">
-        <v>46020</v>
-      </c>
-      <c r="K93" s="1">
-        <v>46079</v>
-      </c>
-      <c r="L93" s="1">
-        <v>46139</v>
-      </c>
-      <c r="M93" t="s">
-        <v>11</v>
-      </c>
-      <c r="N93" s="1">
-        <v>46139</v>
-      </c>
-      <c r="O93" t="s">
-        <v>29</v>
-      </c>
-      <c r="P93">
-        <v>1</v>
-      </c>
-      <c r="Q93" t="s">
-        <v>30</v>
-      </c>
-      <c r="R93">
-        <v>394</v>
-      </c>
-      <c r="S93">
-        <v>20</v>
-      </c>
-      <c r="T93" t="s">
-        <v>281</v>
-      </c>
-      <c r="U93" t="s">
-        <v>374</v>
-      </c>
-      <c r="V93">
-        <v>394</v>
-      </c>
-      <c r="W93" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23">
-      <c r="A94">
-        <v>752</v>
-      </c>
-      <c r="B94" t="s">
-        <v>126</v>
-      </c>
-      <c r="C94" s="1">
-        <v>45959</v>
-      </c>
-      <c r="D94" t="s">
-        <v>24</v>
-      </c>
-      <c r="E94" t="s">
-        <v>143</v>
-      </c>
-      <c r="F94" t="s">
-        <v>26</v>
-      </c>
-      <c r="G94" t="s">
-        <v>27</v>
-      </c>
-      <c r="H94" t="s">
-        <v>28</v>
-      </c>
-      <c r="I94" s="1">
-        <v>45989</v>
-      </c>
-      <c r="J94" s="1">
-        <v>46020</v>
-      </c>
-      <c r="K94" s="1">
-        <v>46079</v>
-      </c>
-      <c r="L94" s="1">
-        <v>46139</v>
-      </c>
-      <c r="M94" t="s">
-        <v>11</v>
-      </c>
-      <c r="N94" s="1">
-        <v>46139</v>
-      </c>
-      <c r="O94" t="s">
-        <v>29</v>
-      </c>
-      <c r="P94">
-        <v>1</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>30</v>
-      </c>
-      <c r="R94">
-        <v>783</v>
-      </c>
-      <c r="S94">
-        <v>52</v>
-      </c>
-      <c r="T94" t="s">
-        <v>282</v>
-      </c>
-      <c r="U94" t="s">
-        <v>375</v>
-      </c>
-      <c r="V94">
-        <v>783</v>
-      </c>
-      <c r="W94" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -8356,7 +7704,7 @@
   <sheetData>
     <row r="1" spans="1:24">
       <c r="A1" t="s">
-        <v>382</v>
+        <v>354</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -8430,13 +7778,13 @@
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="B2">
         <v>766</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="D2" s="1">
         <v>45966</v>
@@ -8445,7 +7793,7 @@
         <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>171</v>
       </c>
       <c r="G2" t="s">
         <v>26</v>
@@ -8481,7 +7829,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="S2">
         <v>151</v>
@@ -8490,27 +7838,27 @@
         <v>151</v>
       </c>
       <c r="U2" t="s">
-        <v>31</v>
+        <v>257</v>
       </c>
       <c r="V2" t="s">
-        <v>32</v>
+        <v>342</v>
       </c>
       <c r="W2">
         <v>151</v>
       </c>
       <c r="X2" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:24">
       <c r="A3" t="s">
-        <v>384</v>
+        <v>356</v>
       </c>
       <c r="B3">
         <v>767</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1">
         <v>45967</v>
@@ -8519,7 +7867,7 @@
         <v>24</v>
       </c>
       <c r="F3" t="s">
-        <v>183</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
         <v>26</v>
@@ -8555,7 +7903,7 @@
         <v>1</v>
       </c>
       <c r="R3" t="s">
-        <v>189</v>
+        <v>30</v>
       </c>
       <c r="S3">
         <v>3864</v>
@@ -8564,21 +7912,21 @@
         <v>3864</v>
       </c>
       <c r="U3" t="s">
-        <v>275</v>
+        <v>31</v>
       </c>
       <c r="V3" t="s">
-        <v>368</v>
+        <v>32</v>
       </c>
       <c r="W3">
         <v>3864</v>
       </c>
       <c r="X3" t="s">
-        <v>381</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:24">
       <c r="A4" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="B4">
         <v>901</v>
@@ -8593,7 +7941,7 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
@@ -8629,7 +7977,7 @@
         <v>1</v>
       </c>
       <c r="R4" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="S4">
         <v>92</v>
@@ -8638,21 +7986,21 @@
         <v>92</v>
       </c>
       <c r="U4" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="V4" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="W4">
         <v>92</v>
       </c>
       <c r="X4" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:24">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="B5">
         <v>900</v>
@@ -8667,7 +8015,7 @@
         <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -8703,7 +8051,7 @@
         <v>1</v>
       </c>
       <c r="R5" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="S5">
         <v>204</v>
@@ -8712,21 +8060,21 @@
         <v>204</v>
       </c>
       <c r="U5" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="V5" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="W5">
         <v>204</v>
       </c>
       <c r="X5" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="6" spans="1:24">
       <c r="A6" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="B6">
         <v>899</v>
@@ -8741,7 +8089,7 @@
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
@@ -8777,7 +8125,7 @@
         <v>1</v>
       </c>
       <c r="R6" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="S6">
         <v>52</v>
@@ -8786,21 +8134,21 @@
         <v>52</v>
       </c>
       <c r="U6" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="V6" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="W6">
         <v>52</v>
       </c>
       <c r="X6" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="7" spans="1:24">
       <c r="A7" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="B7">
         <v>898</v>
@@ -8815,7 +8163,7 @@
         <v>24</v>
       </c>
       <c r="F7" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
         <v>26</v>
@@ -8851,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="R7" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="S7">
         <v>64</v>
@@ -8860,21 +8208,21 @@
         <v>64</v>
       </c>
       <c r="U7" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="V7" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="W7">
         <v>64</v>
       </c>
       <c r="X7" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:24">
       <c r="A8" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="B8">
         <v>897</v>
@@ -8889,7 +8237,7 @@
         <v>24</v>
       </c>
       <c r="F8" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G8" t="s">
         <v>26</v>
@@ -8925,7 +8273,7 @@
         <v>1</v>
       </c>
       <c r="R8" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="S8">
         <v>56</v>
@@ -8934,21 +8282,21 @@
         <v>56</v>
       </c>
       <c r="U8" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="V8" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="W8">
         <v>56</v>
       </c>
       <c r="X8" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:24">
       <c r="A9" t="s">
-        <v>385</v>
+        <v>357</v>
       </c>
       <c r="B9">
         <v>893</v>
@@ -8963,7 +8311,7 @@
         <v>24</v>
       </c>
       <c r="F9" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G9" t="s">
         <v>26</v>
@@ -8999,7 +8347,7 @@
         <v>1</v>
       </c>
       <c r="R9" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="S9">
         <v>7656</v>
@@ -9008,21 +8356,21 @@
         <v>7656</v>
       </c>
       <c r="U9" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="V9" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="W9">
         <v>7656</v>
       </c>
       <c r="X9" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:24">
       <c r="A10" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="B10">
         <v>895</v>
@@ -9037,7 +8385,7 @@
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G10" t="s">
         <v>26</v>
@@ -9073,7 +8421,7 @@
         <v>1</v>
       </c>
       <c r="R10" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="S10">
         <v>18408</v>
@@ -9082,21 +8430,21 @@
         <v>18408</v>
       </c>
       <c r="U10" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="V10" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="W10">
         <v>18408</v>
       </c>
       <c r="X10" t="s">
-        <v>379</v>
+        <v>351</v>
       </c>
     </row>
     <row r="11" spans="1:24">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="B11">
         <v>902</v>
@@ -9111,7 +8459,7 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G11" t="s">
         <v>26</v>
@@ -9147,7 +8495,7 @@
         <v>1</v>
       </c>
       <c r="R11" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="S11">
         <v>2168</v>
@@ -9156,21 +8504,21 @@
         <v>2168</v>
       </c>
       <c r="U11" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="V11" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="W11">
         <v>2168</v>
       </c>
       <c r="X11" t="s">
-        <v>378</v>
+        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:24">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="B12">
         <v>866</v>
@@ -9185,7 +8533,7 @@
         <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="G12" t="s">
         <v>26</v>
@@ -9221,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="R12" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="S12">
         <v>39927</v>
@@ -9230,27 +8578,27 @@
         <v>39927</v>
       </c>
       <c r="U12" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="V12" t="s">
-        <v>324</v>
+        <v>304</v>
       </c>
       <c r="W12">
         <v>39927</v>
       </c>
       <c r="X12" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="13" spans="1:24">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="B13">
         <v>817</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D13" s="1">
         <v>46030</v>
@@ -9259,7 +8607,7 @@
         <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
@@ -9295,36 +8643,36 @@
         <v>1</v>
       </c>
       <c r="R13" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="S13">
-        <v>10238</v>
+        <v>8839</v>
       </c>
       <c r="T13">
-        <v>10238</v>
+        <v>8839</v>
       </c>
       <c r="U13" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="V13" t="s">
-        <v>343</v>
+        <v>318</v>
       </c>
       <c r="W13">
-        <v>10238</v>
+        <v>8839</v>
       </c>
       <c r="X13" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="14" spans="1:24">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="B14">
         <v>769</v>
       </c>
       <c r="C14" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D14" s="1">
         <v>45971</v>
@@ -9333,7 +8681,7 @@
         <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="G14" t="s">
         <v>26</v>
@@ -9369,7 +8717,7 @@
         <v>1</v>
       </c>
       <c r="R14" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="S14">
         <v>2726</v>
@@ -9378,27 +8726,27 @@
         <v>3</v>
       </c>
       <c r="U14" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="V14" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="W14">
         <v>2726</v>
       </c>
       <c r="X14" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" spans="1:24">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>359</v>
       </c>
       <c r="B15">
         <v>768</v>
       </c>
       <c r="C15" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D15" s="1">
         <v>45971</v>
@@ -9407,7 +8755,7 @@
         <v>24</v>
       </c>
       <c r="F15" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G15" t="s">
         <v>26</v>
@@ -9443,7 +8791,7 @@
         <v>1</v>
       </c>
       <c r="R15" t="s">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="S15">
         <v>7746</v>
@@ -9452,16 +8800,16 @@
         <v>6</v>
       </c>
       <c r="U15" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="V15" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="W15">
         <v>7746</v>
       </c>
       <c r="X15" t="s">
-        <v>33</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
